--- a/docs/test-cases/SPM-30_Test_Cases.xlsx
+++ b/docs/test-cases/SPM-30_Test_Cases.xlsx
@@ -1434,7 +1434,7 @@
         </is>
       </c>
     </row>
-    <row r="3" ht="71.5" customHeight="1">
+    <row r="3" ht="112" customHeight="1">
       <c r="A3" s="12" t="inlineStr">
         <is>
           <t>Pre-conditions</t>
@@ -1443,7 +1443,8 @@
       <c r="B3" s="13" t="inlineStr">
         <is>
           <t>SPM-30 fixtures loaded: 'SPM30 Nusantara Developer Meetup' (organiser Budi Santoso, Nusantara Tech Labs) is Submitted with no coordinator.
-Logged in as Grace Lim (grace.lim@connectsphere.com / password123).</t>
+Logged in as Grace Lim (grace.lim@connectsphere.com / password123).
+Data reset: Changes data (assigns the event). TC09 and TC10 continue from this result, so reset only after TC10: run `npm run fixtures:spm30` from the project folder.</t>
         </is>
       </c>
     </row>
@@ -1598,7 +1599,7 @@
         </is>
       </c>
     </row>
-    <row r="3" ht="58" customHeight="1">
+    <row r="3" ht="98.5" customHeight="1">
       <c r="A3" s="12" t="inlineStr">
         <is>
           <t>Pre-conditions</t>
@@ -1607,7 +1608,8 @@
       <c r="B3" s="13" t="inlineStr">
         <is>
           <t>TC08 completed: Daniel Tan is assigned to 'SPM30 Nusantara Developer Meetup'.
-Logged in as Daniel Tan (daniel.tan@connectsphere.com / password123).</t>
+Logged in as Daniel Tan (daniel.tan@connectsphere.com / password123).
+Data reset: Changes data (adds an equipment requirement). Reset after TC10: run `npm run fixtures:spm30` from the project folder.</t>
         </is>
       </c>
     </row>
@@ -1760,7 +1762,7 @@
         </is>
       </c>
     </row>
-    <row r="3" ht="58" customHeight="1">
+    <row r="3" ht="85" customHeight="1">
       <c r="A3" s="12" t="inlineStr">
         <is>
           <t>Pre-conditions</t>
@@ -1769,7 +1771,8 @@
       <c r="B3" s="13" t="inlineStr">
         <is>
           <t>TC08 completed: Daniel Tan is assigned to 'SPM30 Nusantara Developer Meetup'.
-Logged in as Budi Santoso (budi.santoso@nusantaratec.com / password123), the event's organiser.</t>
+Logged in as Budi Santoso (budi.santoso@nusantaratec.com / password123), the event's organiser.
+Data reset: After this case, reset the data TC08 and TC09 changed: run `npm run fixtures:spm30` from the project folder.</t>
         </is>
       </c>
     </row>
@@ -2237,7 +2240,7 @@
         </is>
       </c>
     </row>
-    <row r="3" ht="71.5" customHeight="1">
+    <row r="3" ht="112" customHeight="1">
       <c r="A3" s="12" t="inlineStr">
         <is>
           <t>Pre-conditions</t>
@@ -2246,7 +2249,8 @@
       <c r="B3" s="13" t="inlineStr">
         <is>
           <t>SPM-30 fixtures loaded: 'SPM30 Kirana Regional Offsite' (organiser Faridah Aziz) is Under review with coordinator Priya Raj.
-Logged in as Grace Lim (grace.lim@connectsphere.com / password123).</t>
+Logged in as Grace Lim (grace.lim@connectsphere.com / password123).
+Data reset: Changes data (reassigns the event). TC14 continues from this result, so reset only after TC14: run `npm run fixtures:spm30` from the project folder.</t>
         </is>
       </c>
     </row>
@@ -2402,7 +2406,7 @@
         </is>
       </c>
     </row>
-    <row r="3" ht="31" customHeight="1">
+    <row r="3" ht="58" customHeight="1">
       <c r="A3" s="12" t="inlineStr">
         <is>
           <t>Pre-conditions</t>
@@ -2410,7 +2414,8 @@
       </c>
       <c r="B3" s="13" t="inlineStr">
         <is>
-          <t>TC13 completed: 'SPM30 Kirana Regional Offsite' reassigned from Priya Raj to Joel Fernandez.</t>
+          <t>TC13 completed: 'SPM30 Kirana Regional Offsite' reassigned from Priya Raj to Joel Fernandez.
+Data reset: After this case, reset the data TC13 changed: run `npm run fixtures:spm30` from the project folder.</t>
         </is>
       </c>
     </row>
@@ -2564,7 +2569,7 @@
         </is>
       </c>
     </row>
-    <row r="3" ht="71.5" customHeight="1">
+    <row r="3" ht="112" customHeight="1">
       <c r="A3" s="12" t="inlineStr">
         <is>
           <t>Pre-conditions</t>
@@ -2573,7 +2578,8 @@
       <c r="B3" s="13" t="inlineStr">
         <is>
           <t>SPM-30 fixtures loaded: 'SPM30 Nusantara Product Launch' (organiser Sari Widodo) is Under review with coordinator Daniel Tan.
-Logged in as Nadia Rahman (nadia.rahman@connectsphere.com / password123), Event Operations Manager.</t>
+Logged in as Nadia Rahman (nadia.rahman@connectsphere.com / password123), Event Operations Manager.
+Data reset: Changes data (reassigns the event). After this case, reset it: run `npm run fixtures:spm30` from the project folder.</t>
         </is>
       </c>
     </row>
@@ -2729,7 +2735,7 @@
         </is>
       </c>
     </row>
-    <row r="3" ht="71.5" customHeight="1">
+    <row r="3" ht="112" customHeight="1">
       <c r="A3" s="12" t="inlineStr">
         <is>
           <t>Pre-conditions</t>
@@ -2738,7 +2744,8 @@
       <c r="B3" s="13" t="inlineStr">
         <is>
           <t>SPM-30 fixtures loaded: 'SPM30 Anchorpoint Partner Briefing' is Confirmed with coordinator Joel Fernandez; 'SPM30 Civic Trust Workshop' is Postponed with coordinator Arif Mansor.
-Logged in as Grace Lim (grace.lim@connectsphere.com / password123).</t>
+Logged in as Grace Lim (grace.lim@connectsphere.com / password123).
+Data reset: Changes data (reassigns both events). After this case, reset them: run `npm run fixtures:spm30` from the project folder.</t>
         </is>
       </c>
     </row>
@@ -3559,7 +3566,7 @@
         </is>
       </c>
     </row>
-    <row r="3" ht="71.5" customHeight="1">
+    <row r="3" ht="139" customHeight="1">
       <c r="A3" s="12" t="inlineStr">
         <is>
           <t>Pre-conditions</t>
@@ -3569,7 +3576,8 @@
         <is>
           <t>Run on a Neon branch or local database, not the shared one.
 Every event in the 'Awaiting assignment' list has been assigned, so no submitted event is unassigned.
-Logged in as Grace Lim (grace.lim@connectsphere.com / password123).</t>
+Logged in as Grace Lim (grace.lim@connectsphere.com / password123).
+Data reset: Changes data on the branch (every submitted event gets a coordinator, including base-seed events the SPM-30 reset does not cover). Afterwards, reset that branch with `npx prisma db seed` then `npm run fixtures:spm30`, or delete the branch. Never reseed the shared database.</t>
         </is>
       </c>
     </row>

--- a/docs/test-cases/SPM-30_Test_Cases.xlsx
+++ b/docs/test-cases/SPM-30_Test_Cases.xlsx
@@ -1434,7 +1434,7 @@
         </is>
       </c>
     </row>
-    <row r="3" ht="112" customHeight="1">
+    <row r="3" ht="125.5" customHeight="1">
       <c r="A3" s="12" t="inlineStr">
         <is>
           <t>Pre-conditions</t>
@@ -1442,7 +1442,8 @@
       </c>
       <c r="B3" s="13" t="inlineStr">
         <is>
-          <t>SPM-30 fixtures loaded: 'SPM30 Nusantara Developer Meetup' (organiser Budi Santoso, Nusantara Tech Labs) is Submitted with no coordinator.
+          <t>Test data loaded: run `npm run fixtures:spm30` from the project folder if it has not been run for this test pass.
+'SPM30 Nusantara Developer Meetup' (organiser Budi Santoso, Nusantara Tech Labs) is Submitted with no coordinator.
 Logged in as Grace Lim (grace.lim@connectsphere.com / password123).
 Data reset: Changes data (assigns the event). TC09 and TC10 continue from this result, so reset only after TC10: run `npm run fixtures:spm30` from the project folder.</t>
         </is>
@@ -1476,7 +1477,7 @@
         </is>
       </c>
     </row>
-    <row r="6" ht="85" customHeight="1">
+    <row r="6" ht="112" customHeight="1">
       <c r="A6" s="12" t="inlineStr">
         <is>
           <t>Expected Result</t>
@@ -1484,7 +1485,7 @@
       </c>
       <c r="B6" s="13" t="inlineStr">
         <is>
-          <t>A success message confirming the assignment is shown.
+          <t>The message 'Daniel Tan is now the coordinator for "SPM30 Nusantara Developer Meetup". It has moved to Under review.' is shown.
 'SPM30 Nusantara Developer Meetup' disappears from the 'Awaiting assignment' list.
 After reloading the event page, the status badge shows 'Under review' (previously 'Submitted') and the 'Details' card shows Coordinator 'Daniel Tan'.</t>
         </is>
@@ -1784,7 +1785,7 @@
       </c>
       <c r="B4" s="13" t="inlineStr">
         <is>
-          <t>1. Click 'All Events'
+          <t>1. Click 'My Events' in the sidebar
 2. Open 'SPM30 Nusantara Developer Meetup'</t>
         </is>
       </c>
@@ -1922,7 +1923,7 @@
         </is>
       </c>
     </row>
-    <row r="3" ht="71.5" customHeight="1">
+    <row r="3" ht="85" customHeight="1">
       <c r="A3" s="12" t="inlineStr">
         <is>
           <t>Pre-conditions</t>
@@ -1930,7 +1931,8 @@
       </c>
       <c r="B3" s="13" t="inlineStr">
         <is>
-          <t>SPM-30 fixtures loaded: 'SPM30 Meridian Client Forum' (owned by James Koh, Meridian Financial Group) is Confirmed with coordinator Daniel Tan.
+          <t>Test data loaded: run `npm run fixtures:spm30` from the project folder if it has not been run for this test pass.
+'SPM30 Meridian Client Forum' (owned by James Koh, Meridian Financial Group) is Confirmed with coordinator Daniel Tan.
 Logged in as Rachel Ng (rachel.ng@meridianfina.com / password123), another organiser at Meridian Financial Group.</t>
         </is>
       </c>
@@ -1943,7 +1945,7 @@
       </c>
       <c r="B4" s="13" t="inlineStr">
         <is>
-          <t>1. Click 'All Events'
+          <t>1. Click 'My Events' in the sidebar
 2. Open 'SPM30 Meridian Client Forum'</t>
         </is>
       </c>
@@ -2081,7 +2083,7 @@
         </is>
       </c>
     </row>
-    <row r="3" ht="58" customHeight="1">
+    <row r="3" ht="85" customHeight="1">
       <c r="A3" s="12" t="inlineStr">
         <is>
           <t>Pre-conditions</t>
@@ -2089,7 +2091,8 @@
       </c>
       <c r="B3" s="13" t="inlineStr">
         <is>
-          <t>SPM-30 fixtures loaded: 'SPM30 Meridian Client Forum' is Confirmed, registration enabled, coordinator Daniel Tan.
+          <t>Test data loaded: run `npm run fixtures:spm30` from the project folder if it has not been run for this test pass.
+'SPM30 Meridian Client Forum' is Confirmed, registration enabled, coordinator Daniel Tan.
 Logged in as an Attendee (lee.wei.ming@example.com / password123).</t>
         </is>
       </c>
@@ -2240,7 +2243,7 @@
         </is>
       </c>
     </row>
-    <row r="3" ht="112" customHeight="1">
+    <row r="3" ht="125.5" customHeight="1">
       <c r="A3" s="12" t="inlineStr">
         <is>
           <t>Pre-conditions</t>
@@ -2248,13 +2251,14 @@
       </c>
       <c r="B3" s="13" t="inlineStr">
         <is>
-          <t>SPM-30 fixtures loaded: 'SPM30 Kirana Regional Offsite' (organiser Faridah Aziz) is Under review with coordinator Priya Raj.
+          <t>Test data loaded: run `npm run fixtures:spm30` from the project folder if it has not been run for this test pass.
+'SPM30 Kirana Regional Offsite' (organiser Faridah Aziz) is Under review with coordinator Priya Raj.
 Logged in as Grace Lim (grace.lim@connectsphere.com / password123).
 Data reset: Changes data (reassigns the event). TC14 continues from this result, so reset only after TC14: run `npm run fixtures:spm30` from the project folder.</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="85" customHeight="1">
+    <row r="4" ht="112" customHeight="1">
       <c r="A4" s="12" t="inlineStr">
         <is>
           <t>Test Steps</t>
@@ -2264,9 +2268,9 @@
         <is>
           <t>1. Click 'All Events'
 2. Open 'SPM30 Kirana Regional Offsite'
-3. Choose the option to change the coordinator
-4. Select 'Joel Fernandez'
-5. Confirm the change
+3. In the 'Change coordinator' card, choose 'Joel Fernandez' from the dropdown
+4. Click 'Reassign'
+5. Click 'Reassign' in the 'Reassign this event?' confirmation
 6. Reload the page</t>
         </is>
       </c>
@@ -2283,7 +2287,7 @@
         </is>
       </c>
     </row>
-    <row r="6" ht="58" customHeight="1">
+    <row r="6" ht="98.5" customHeight="1">
       <c r="A6" s="12" t="inlineStr">
         <is>
           <t>Expected Result</t>
@@ -2291,7 +2295,8 @@
       </c>
       <c r="B6" s="13" t="inlineStr">
         <is>
-          <t>A success message confirming the reassignment is shown.
+          <t>The confirmation says the event moves from Priya Raj to Joel Fernandez.
+The message 'Reassigned from Priya Raj to Joel Fernandez.' is shown.
 After reloading, the 'Details' card shows Coordinator 'Joel Fernandez'.
 The event status is unchanged (Under review).</t>
         </is>
@@ -2569,7 +2574,7 @@
         </is>
       </c>
     </row>
-    <row r="3" ht="112" customHeight="1">
+    <row r="3" ht="125.5" customHeight="1">
       <c r="A3" s="12" t="inlineStr">
         <is>
           <t>Pre-conditions</t>
@@ -2577,13 +2582,14 @@
       </c>
       <c r="B3" s="13" t="inlineStr">
         <is>
-          <t>SPM-30 fixtures loaded: 'SPM30 Nusantara Product Launch' (organiser Sari Widodo) is Under review with coordinator Daniel Tan.
+          <t>Test data loaded: run `npm run fixtures:spm30` from the project folder if it has not been run for this test pass.
+'SPM30 Nusantara Product Launch' (organiser Sari Widodo) is Under review with coordinator Daniel Tan.
 Logged in as Nadia Rahman (nadia.rahman@connectsphere.com / password123), Event Operations Manager.
 Data reset: Changes data (reassigns the event). After this case, reset it: run `npm run fixtures:spm30` from the project folder.</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="112" customHeight="1">
+    <row r="4" ht="125.5" customHeight="1">
       <c r="A4" s="12" t="inlineStr">
         <is>
           <t>Test Steps</t>
@@ -2592,11 +2598,12 @@
       <c r="B4" s="13" t="inlineStr">
         <is>
           <t>1. Click 'Assignments' in the sidebar
-2. Switch to the view listing events that already have a coordinator
+2. Click the 'Assigned' tab
 3. Find the row for 'SPM30 Nusantara Product Launch'
-4. Choose 'Hui Shan Neo' as the new coordinator
-5. Confirm the change
-6. Click 'All Events' and open 'SPM30 Nusantara Product Launch'</t>
+4. In that row's dropdown, choose 'Hui Shan Neo'
+5. Click 'Reassign' in that row
+6. Click 'Reassign' in the 'Reassign this event?' confirmation
+7. Click 'All Events' and open 'SPM30 Nusantara Product Launch'</t>
         </is>
       </c>
     </row>
@@ -2612,7 +2619,7 @@
         </is>
       </c>
     </row>
-    <row r="6" ht="44.5" customHeight="1">
+    <row r="6" ht="58" customHeight="1">
       <c r="A6" s="12" t="inlineStr">
         <is>
           <t>Expected Result</t>
@@ -2620,7 +2627,7 @@
       </c>
       <c r="B6" s="13" t="inlineStr">
         <is>
-          <t>A success message confirming the reassignment is shown.
+          <t>The message '"SPM30 Nusantara Product Launch" has been reassigned from Daniel Tan to Hui Shan Neo.' is shown.
 The event page shows Coordinator 'Hui Shan Neo'.
 The event status is unchanged (Under review).</t>
         </is>
@@ -2735,7 +2742,7 @@
         </is>
       </c>
     </row>
-    <row r="3" ht="112" customHeight="1">
+    <row r="3" ht="139" customHeight="1">
       <c r="A3" s="12" t="inlineStr">
         <is>
           <t>Pre-conditions</t>
@@ -2743,13 +2750,14 @@
       </c>
       <c r="B3" s="13" t="inlineStr">
         <is>
-          <t>SPM-30 fixtures loaded: 'SPM30 Anchorpoint Partner Briefing' is Confirmed with coordinator Joel Fernandez; 'SPM30 Civic Trust Workshop' is Postponed with coordinator Arif Mansor.
+          <t>Test data loaded: run `npm run fixtures:spm30` from the project folder if it has not been run for this test pass.
+'SPM30 Anchorpoint Partner Briefing' is Confirmed with coordinator Joel Fernandez; 'SPM30 Civic Trust Workshop' is Postponed with coordinator Arif Mansor.
 Logged in as Grace Lim (grace.lim@connectsphere.com / password123).
 Data reset: Changes data (reassigns both events). After this case, reset them: run `npm run fixtures:spm30` from the project folder.</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="71.5" customHeight="1">
+    <row r="4" ht="98.5" customHeight="1">
       <c r="A4" s="12" t="inlineStr">
         <is>
           <t>Test Steps</t>
@@ -2759,9 +2767,9 @@
         <is>
           <t>1. Click 'All Events'
 2. Open 'SPM30 Anchorpoint Partner Briefing'
-3. Change the coordinator to 'Arif Mansor' and confirm
-4. Open 'SPM30 Civic Trust Workshop'
-5. Change the coordinator to 'Hui Shan Neo' and confirm</t>
+3. In the 'Change coordinator' card, choose 'Arif Mansor', click 'Reassign', then 'Reassign' in the confirmation
+4. Click 'All Events' and open 'SPM30 Civic Trust Workshop'
+5. In the 'Change coordinator' card, choose 'Hui Shan Neo', click 'Reassign', then 'Reassign' in the confirmation</t>
         </is>
       </c>
     </row>
@@ -2900,7 +2908,7 @@
         </is>
       </c>
     </row>
-    <row r="3" ht="85" customHeight="1">
+    <row r="3" ht="112" customHeight="1">
       <c r="A3" s="12" t="inlineStr">
         <is>
           <t>Pre-conditions</t>
@@ -2908,7 +2916,8 @@
       </c>
       <c r="B3" s="13" t="inlineStr">
         <is>
-          <t>SPM-30 fixtures loaded: 'SPM30 Harbourline Claims Training' is Completed (Priya Raj), 'SPM30 Pearl Delta Supplier Forum' is Cancelled (Joel Fernandez), 'SPM30 Selaras Overnight Field Day' is Rejected (Priya Raj).
+          <t>Test data loaded: run `npm run fixtures:spm30` from the project folder if it has not been run for this test pass.
+'SPM30 Harbourline Claims Training' is Completed (Priya Raj), 'SPM30 Pearl Delta Supplier Forum' is Cancelled (Joel Fernandez), 'SPM30 Selaras Overnight Field Day' is Rejected (Priya Raj).
 Logged in as Grace Lim (grace.lim@connectsphere.com / password123).</t>
         </is>
       </c>
@@ -2922,10 +2931,10 @@
       <c r="B4" s="13" t="inlineStr">
         <is>
           <t>1. Click 'All Events'
-2. Open 'SPM30 Harbourline Claims Training' and look for an option to change the coordinator
-3. Open 'SPM30 Pearl Delta Supplier Forum' and look for an option to change the coordinator
-4. Open 'SPM30 Selaras Overnight Field Day' and look for an option to change the coordinator
-5. Click 'Assignments' and check whether any of these three events are listed</t>
+2. Open 'SPM30 Harbourline Claims Training' and look for a 'Change coordinator' card
+3. Open 'SPM30 Pearl Delta Supplier Forum' and look for a 'Change coordinator' card
+4. Open 'SPM30 Selaras Overnight Field Day' and look for a 'Change coordinator' card
+5. Click 'Assignments', open the 'Assigned' tab, and check whether any of these three events are listed</t>
         </is>
       </c>
     </row>
@@ -2941,7 +2950,7 @@
         </is>
       </c>
     </row>
-    <row r="6" ht="58" customHeight="1">
+    <row r="6" ht="44.5" customHeight="1">
       <c r="A6" s="12" t="inlineStr">
         <is>
           <t>Expected Result</t>
@@ -2949,8 +2958,8 @@
       </c>
       <c r="B6" s="13" t="inlineStr">
         <is>
-          <t>No option to change the coordinator is shown on any of the three events.
-None of them appear on the Assignments page.
+          <t>None of the three events shows a 'Change coordinator' card.
+None of them appear on either Assignments tab.
 Each still shows its original coordinator.</t>
         </is>
       </c>
@@ -3037,7 +3046,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C14"/>
+  <dimension ref="A1:C5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -3062,148 +3071,49 @@
         </is>
       </c>
     </row>
-    <row r="2" ht="71.5" customHeight="1">
+    <row r="2" ht="58" customHeight="1">
       <c r="A2" s="11" t="n">
         <v>1</v>
       </c>
       <c r="B2" s="11" t="inlineStr">
         <is>
-          <t>NOTE: SPM-30 is not implemented yet. The Assignments page (src/app/assignments/page.tsx) is a 'not built yet' placeholder and there is no assignment endpoint. Steps follow the S-28 Assignment Queue mockup (design/mockups/AssignmentQueue.dc.html) and must be re-checked against the built UI (button labels, messages, reassign controls).</t>
+          <t>NOTE: Test data comes from scripts/seed-spm30.ts (npm run fixtures:spm30). It only deletes and recreates events whose seed key starts with 'spm30_'; the rest of the database is untouched. Run it before a full pass, and wherever a case's 'Data reset' line says to.</t>
         </is>
       </c>
       <c r="C2" s="11" t="n"/>
     </row>
-    <row r="3" ht="71.5" customHeight="1">
+    <row r="3" ht="98.5" customHeight="1">
       <c r="A3" s="11" t="n">
         <v>2</v>
       </c>
       <c r="B3" s="11" t="inlineStr">
         <is>
-          <t>NOTE: Test data comes from scripts/seed-spm30.ts (npm run fixtures:spm30). It only deletes and recreates events whose seed key starts with 'spm30_'; the rest of the database is untouched. Run it before a full pass (TC01-TC19 run in order from fresh fixtures) and again afterwards to reset.</t>
+          <t>NOTE: TC20 (empty state) runs on the shared database. It assigns the two base-seed events that start in the queue, so it must run last and be followed by `npm run fixtures:spm30`, which puts them back (if another story has since moved one past Under review, the script leaves it and says so; `-- --restore-queue` forces it). If the queue holds any other event (e.g. one a teammate created in the app), TC20 says to stop rather than assign it, because the script cannot restore it.</t>
         </is>
       </c>
       <c r="C3" s="11" t="n"/>
     </row>
-    <row r="4" ht="58" customHeight="1">
+    <row r="4" ht="31" customHeight="1">
       <c r="A4" s="11" t="n">
         <v>3</v>
       </c>
       <c r="B4" s="11" t="inlineStr">
         <is>
-          <t>NOTE: TC20 (empty state) needs zero unassigned submitted events in the whole database, which on the shared database means assigning base-seed events such as 'Nusantara Developer Summit'. The fixture script does not restore those. Run TC20 on a Neon branch or local database.</t>
+          <t>NOTE: Organisers from an unrelated company not seeing the event is covered by SPM-31 (visibility), so it is not repeated here.</t>
         </is>
       </c>
       <c r="C4" s="11" t="n"/>
     </row>
-    <row r="5" ht="31" customHeight="1">
+    <row r="5" ht="58" customHeight="1">
       <c r="A5" s="11" t="n">
         <v>4</v>
       </c>
       <c r="B5" s="11" t="inlineStr">
         <is>
-          <t>NOTE: Organisers from an unrelated company not seeing the event is covered by SPM-31 (visibility), so it is not repeated here.</t>
+          <t>OPEN: Notifications are written on assignment (new coordinator) and reassignment (new and previous coordinator), but there are no test cases for them yet because the Notifications page (S-04, SPM-53) is still a placeholder. Add them once SPM-53 is built.</t>
         </is>
       </c>
       <c r="C5" s="11" t="n"/>
-    </row>
-    <row r="6" ht="31" customHeight="1">
-      <c r="A6" s="11" t="n">
-        <v>5</v>
-      </c>
-      <c r="B6" s="11" t="inlineStr">
-        <is>
-          <t>RESOLVED 2026-09-28: Only the Event Operations Manager can assign or reassign a coordinator (no self-assignment).</t>
-        </is>
-      </c>
-      <c r="C6" s="11" t="n"/>
-    </row>
-    <row r="7" ht="58" customHeight="1">
-      <c r="A7" s="11" t="n">
-        <v>6</v>
-      </c>
-      <c r="B7" s="11" t="inlineStr">
-        <is>
-          <t>RESOLVED 2026-09-28: Assigning a coordinator moves the event from Submitted to Under review (TC08). So a Submitted event never has a coordinator, and filtering the Ops Manager dashboard's 'Awaiting assignment' section on status Submitted is enough.</t>
-        </is>
-      </c>
-      <c r="C7" s="11" t="n"/>
-    </row>
-    <row r="8" ht="58" customHeight="1">
-      <c r="A8" s="11" t="n">
-        <v>7</v>
-      </c>
-      <c r="B8" s="11" t="inlineStr">
-        <is>
-          <t>RESOLVED 2026-09-28: Reassignment is available from both the event detail page (TC13) and the Assignments page (TC15). The mockup has no Assignments view for already-assigned events yet; re-check TC15's steps once built.</t>
-        </is>
-      </c>
-      <c r="C8" s="11" t="n"/>
-    </row>
-    <row r="9" ht="44.5" customHeight="1">
-      <c r="A9" s="11" t="n">
-        <v>8</v>
-      </c>
-      <c r="B9" s="11" t="inlineStr">
-        <is>
-          <t>RESOLVED 2026-09-28: Events can be reassigned in any active status (Under review, Approved, Planning, Confirmed, Postponed), not Completed, Cancelled or Rejected (TC16, TC17).</t>
-        </is>
-      </c>
-      <c r="C9" s="11" t="n"/>
-    </row>
-    <row r="10" ht="44.5" customHeight="1">
-      <c r="A10" s="11" t="n">
-        <v>9</v>
-      </c>
-      <c r="B10" s="11" t="inlineStr">
-        <is>
-          <t>RESOLVED 2026-09-28: The owning organiser and organisers from the same client organisation see the assigned coordinator at any non-draft status, with 'Not yet assigned' shown until then (TC06, TC10, TC11).</t>
-        </is>
-      </c>
-      <c r="C10" s="11" t="n"/>
-    </row>
-    <row r="11" ht="58" customHeight="1">
-      <c r="A11" s="11" t="n">
-        <v>10</v>
-      </c>
-      <c r="B11" s="11" t="inlineStr">
-        <is>
-          <t>RESOLVED 2026-09-28: Remove the 'any coordinator can manage an unassigned event' allowance (TC07). This requires changing isAssignedCoordinator in src/lib/permissions.ts and updating docs/PERMISSIONS.md ('Assigned' relationship and Open items).</t>
-        </is>
-      </c>
-      <c r="C11" s="11" t="n"/>
-    </row>
-    <row r="12" ht="71.5" customHeight="1">
-      <c r="A12" s="11" t="n">
-        <v>11</v>
-      </c>
-      <c r="B12" s="11" t="inlineStr">
-        <is>
-          <t>RESOLVED 2026-09-28: On assignment the new coordinator is notified; on reassignment both the new and previous coordinators are notified; the organiser is not notified. No test cases yet because the Notifications page (S-04, SPM-53) is still a placeholder, so a tester cannot see notifications on screen. Add them once SPM-53 is built.</t>
-        </is>
-      </c>
-      <c r="C12" s="11" t="n"/>
-    </row>
-    <row r="13" ht="85" customHeight="1">
-      <c r="A13" s="11" t="n">
-        <v>12</v>
-      </c>
-      <c r="B13" s="11" t="inlineStr">
-        <is>
-          <t>RESOLVED 2026-09-28: The mockup's 'Coordinator workload' panel is not a requirement. Customer clarification #93: choosing a coordinator 'is up to Event Operations Manager, they have their own SOP which is handled outside of the system'. #92: a coordinator can be assigned to multiple events concurrently (no cap). No Jira story covers it. Out of scope for SPM-30; no test cases.</t>
-        </is>
-      </c>
-      <c r="C13" s="11" t="n"/>
-    </row>
-    <row r="14" ht="112" customHeight="1">
-      <c r="A14" s="11" t="n">
-        <v>13</v>
-      </c>
-      <c r="B14" s="11" t="inlineStr">
-        <is>
-          <t>CONFIRMED by customer clarifications (docs/discussions/20260916): #94 and #101 - only the Event Operations Manager assigns and reassigns, as a separate role, and reassignment approval happens outside the system; #95 - no acceptance step, the assignment takes effect immediately (TC09); #81 - organisers in the same client organisation may view each other's events (TC11); #117 - the Ops Manager must be able to identify newly submitted events needing assignment, without a notification per submission (TC01, TC02).</t>
-        </is>
-      </c>
-      <c r="C14" s="11" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -3243,7 +3153,7 @@
         </is>
       </c>
     </row>
-    <row r="3" ht="58" customHeight="1">
+    <row r="3" ht="85" customHeight="1">
       <c r="A3" s="12" t="inlineStr">
         <is>
           <t>Pre-conditions</t>
@@ -3251,7 +3161,8 @@
       </c>
       <c r="B3" s="13" t="inlineStr">
         <is>
-          <t>SPM-30 fixtures loaded: 'SPM30 Straits Journal Club' is Under review with coordinator Joel Fernandez.
+          <t>Test data loaded: run `npm run fixtures:spm30` from the project folder if it has not been run for this test pass.
+'SPM30 Straits Journal Club' is Under review with coordinator Joel Fernandez.
 Logged in as Grace Lim (grace.lim@connectsphere.com / password123).</t>
         </is>
       </c>
@@ -3266,8 +3177,7 @@
         <is>
           <t>1. Click 'All Events'
 2. Open 'SPM30 Straits Journal Club'
-3. Choose the option to change the coordinator
-4. Select 'Joel Fernandez' (the current coordinator)</t>
+3. In the 'Change coordinator' card, choose 'Joel Fernandez' (the current coordinator) from the dropdown</t>
         </is>
       </c>
     </row>
@@ -3283,7 +3193,7 @@
         </is>
       </c>
     </row>
-    <row r="6" ht="44.5" customHeight="1">
+    <row r="6" ht="58" customHeight="1">
       <c r="A6" s="12" t="inlineStr">
         <is>
           <t>Expected Result</t>
@@ -3291,7 +3201,8 @@
       </c>
       <c r="B6" s="13" t="inlineStr">
         <is>
-          <t>The confirm button is disabled, or a message says Joel Fernandez is already the assigned coordinator.
+          <t>The message 'Joel Fernandez is already the assigned coordinator.' appears under the dropdown.
+The 'Reassign' button stays disabled.
 The coordinator remains 'Joel Fernandez'.</t>
         </is>
       </c>
@@ -3405,7 +3316,7 @@
         </is>
       </c>
     </row>
-    <row r="3" ht="44.5" customHeight="1">
+    <row r="3" ht="58" customHeight="1">
       <c r="A3" s="12" t="inlineStr">
         <is>
           <t>Pre-conditions</t>
@@ -3413,7 +3324,8 @@
       </c>
       <c r="B3" s="13" t="inlineStr">
         <is>
-          <t>SPM-30 fixtures loaded: 'SPM30 Straits Journal Club' is Under review with coordinator Joel Fernandez (organiser Raj Kumar).</t>
+          <t>Test data loaded: run `npm run fixtures:spm30` from the project folder if it has not been run for this test pass.
+'SPM30 Straits Journal Club' is Under review with coordinator Joel Fernandez (organiser Raj Kumar).</t>
         </is>
       </c>
     </row>
@@ -3426,9 +3338,9 @@
       <c r="B4" s="13" t="inlineStr">
         <is>
           <t>1. Log in as Joel Fernandez (joel.fernandez@connectsphere.com / password123)
-2. Open 'SPM30 Straits Journal Club' and look for an option to change the coordinator
+2. Click 'All Events', open 'SPM30 Straits Journal Club' and look for a 'Change coordinator' card
 3. Log out and log in as Raj Kumar (raj.kumar@straitsmedic.com / password123)
-4. Open 'SPM30 Straits Journal Club' and look for an option to change the coordinator</t>
+4. Click 'My Events', open 'SPM30 Straits Journal Club' and look for a 'Change coordinator' card</t>
         </is>
       </c>
     </row>
@@ -3452,8 +3364,8 @@
       </c>
       <c r="B6" s="13" t="inlineStr">
         <is>
-          <t>Neither user sees any option to assign or change the coordinator.
-The Coordinator row shows 'Joel Fernandez' as read-only text.</t>
+          <t>Neither user sees a 'Change coordinator' card or any other way to assign or change the coordinator.
+The 'Details' card shows Coordinator 'Joel Fernandez' as read-only text.</t>
         </is>
       </c>
     </row>
@@ -3566,7 +3478,7 @@
         </is>
       </c>
     </row>
-    <row r="3" ht="139" customHeight="1">
+    <row r="3" ht="152.5" customHeight="1">
       <c r="A3" s="12" t="inlineStr">
         <is>
           <t>Pre-conditions</t>
@@ -3574,14 +3486,14 @@
       </c>
       <c r="B3" s="13" t="inlineStr">
         <is>
-          <t>Run on a Neon branch or local database, not the shared one.
-Every event in the 'Awaiting assignment' list has been assigned, so no submitted event is unassigned.
+          <t>Test data freshly loaded: run `npm run fixtures:spm30` from the project folder just before this case.
+Run this case last in the pass: it assigns every event waiting for a coordinator, including two base-seed events other stories' test cases rely on.
 Logged in as Grace Lim (grace.lim@connectsphere.com / password123).
-Data reset: Changes data on the branch (every submitted event gets a coordinator, including base-seed events the SPM-30 reset does not cover). Afterwards, reset that branch with `npx prisma db seed` then `npm run fixtures:spm30`, or delete the branch. Never reseed the shared database.</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="17.5" customHeight="1">
+Data reset: after this case, run `npm run fixtures:spm30` from the project folder. It resets the SPM30 events and puts 'Nusantara Developer Summit' and 'Meridian Graduate Recruitment Evening' back to Submitted with no coordinator.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="98.5" customHeight="1">
       <c r="A4" s="12" t="inlineStr">
         <is>
           <t>Test Steps</t>
@@ -3589,11 +3501,14 @@
       </c>
       <c r="B4" s="13" t="inlineStr">
         <is>
-          <t>1. Click 'Assignments' in the sidebar</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="17.5" customHeight="1">
+          <t>1. Click 'Assignments' in the sidebar
+2. Check the 'Awaiting assignment' list contains only the four expected events (see test data); if it lists any other event, stop and do not assign it
+3. For each event in the list, choose 'Daniel Tan' in its 'Assign to' dropdown and click 'Assign'
+4. Reload the page</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="58" customHeight="1">
       <c r="A5" s="12" t="inlineStr">
         <is>
           <t>Test Data</t>
@@ -3601,11 +3516,11 @@
       </c>
       <c r="B5" s="13" t="inlineStr">
         <is>
-          <t>Unassigned submitted events: 0</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="44.5" customHeight="1">
+          <t>Expected queue before assigning (4 events): SPM30 Nusantara Developer Meetup, SPM30 Meridian Graduate Evening, Nusantara Developer Summit, Meridian Graduate Recruitment Evening | Coordinator for all: Daniel Tan</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="71.5" customHeight="1">
       <c r="A6" s="12" t="inlineStr">
         <is>
           <t>Expected Result</t>
@@ -3613,7 +3528,7 @@
       </c>
       <c r="B6" s="13" t="inlineStr">
         <is>
-          <t>An empty-state message is shown saying there are no events awaiting assignment.
+          <t>After the last assignment, and again after reloading, the 'Awaiting assignment' tab shows the message 'No events are awaiting assignment' with 'Every submitted event has a coordinator.'
 No table rows and no error are shown.</t>
         </is>
       </c>
@@ -3727,7 +3642,7 @@
         </is>
       </c>
     </row>
-    <row r="3" ht="44.5" customHeight="1">
+    <row r="3" ht="58" customHeight="1">
       <c r="A3" s="12" t="inlineStr">
         <is>
           <t>Pre-conditions</t>
@@ -3735,12 +3650,12 @@
       </c>
       <c r="B3" s="13" t="inlineStr">
         <is>
-          <t>SPM-30 fixtures freshly loaded (npm run fixtures:spm30).
+          <t>Test data freshly loaded: run `npm run fixtures:spm30` from the project folder just before this case.
 Logged in as Grace Lim (grace.lim@connectsphere.com / password123), Event Operations Manager.</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="17.5" customHeight="1">
+    <row r="4" ht="44.5" customHeight="1">
       <c r="A4" s="12" t="inlineStr">
         <is>
           <t>Test Steps</t>
@@ -3748,7 +3663,8 @@
       </c>
       <c r="B4" s="13" t="inlineStr">
         <is>
-          <t>1. Click 'Assignments' in the sidebar</t>
+          <t>1. Click 'Assignments' in the sidebar
+2. Click 'SPM30 Meridian Graduate Evening' in the list to open it</t>
         </is>
       </c>
     </row>
@@ -3764,7 +3680,7 @@
         </is>
       </c>
     </row>
-    <row r="6" ht="98.5" customHeight="1">
+    <row r="6" ht="152.5" customHeight="1">
       <c r="A6" s="12" t="inlineStr">
         <is>
           <t>Expected Result</t>
@@ -3772,10 +3688,10 @@
       </c>
       <c r="B6" s="13" t="inlineStr">
         <is>
-          <t>The 'Awaiting assignment' table shows 'SPM30 Nusantara Developer Meetup' and 'SPM30 Meridian Graduate Evening' with their client, date and how long they have been waiting.
+          <t>The 'Awaiting assignment' table shows 'SPM30 Nusantara Developer Meetup' and 'SPM30 Meridian Graduate Evening' with their client, date and how long they have been waiting. Base-seed events that are also submitted with no coordinator (e.g. 'Nusantara Developer Summit', 'Meridian Graduate Recruitment Evening') may appear too.
 'SPM30 Kirana Regional Offsite' (already has a coordinator) is not listed.
 'SPM30 Draft Investor Update' (draft) is not listed.
-Every row shown has status Submitted.</t>
+The opened event's page shows the 'Submitted' status badge next to its title, and Coordinator 'Not yet assigned'.</t>
         </is>
       </c>
     </row>
@@ -3888,7 +3804,7 @@
         </is>
       </c>
     </row>
-    <row r="3" ht="44.5" customHeight="1">
+    <row r="3" ht="58" customHeight="1">
       <c r="A3" s="12" t="inlineStr">
         <is>
           <t>Pre-conditions</t>
@@ -3896,7 +3812,7 @@
       </c>
       <c r="B3" s="13" t="inlineStr">
         <is>
-          <t>SPM-30 fixtures freshly loaded.
+          <t>Test data freshly loaded: run `npm run fixtures:spm30` from the project folder just before this case.
 Logged in as Nadia Rahman (nadia.rahman@connectsphere.com / password123), Event Operations Manager.</t>
         </is>
       </c>
@@ -4214,7 +4130,7 @@
         </is>
       </c>
     </row>
-    <row r="3" ht="44.5" customHeight="1">
+    <row r="3" ht="58" customHeight="1">
       <c r="A3" s="12" t="inlineStr">
         <is>
           <t>Pre-conditions</t>
@@ -4222,7 +4138,7 @@
       </c>
       <c r="B3" s="13" t="inlineStr">
         <is>
-          <t>SPM-30 fixtures loaded.
+          <t>Test data loaded: run `npm run fixtures:spm30` from the project folder if it has not been run for this test pass.
 Logged in as Grace Lim (grace.lim@connectsphere.com / password123).</t>
         </is>
       </c>
@@ -4374,7 +4290,7 @@
         </is>
       </c>
     </row>
-    <row r="3" ht="58" customHeight="1">
+    <row r="3" ht="85" customHeight="1">
       <c r="A3" s="12" t="inlineStr">
         <is>
           <t>Pre-conditions</t>
@@ -4382,7 +4298,8 @@
       </c>
       <c r="B3" s="13" t="inlineStr">
         <is>
-          <t>SPM-30 fixtures loaded: 'SPM30 Meridian Graduate Evening' is Submitted with no coordinator.
+          <t>Test data loaded: run `npm run fixtures:spm30` from the project folder if it has not been run for this test pass.
+'SPM30 Meridian Graduate Evening' is Submitted with no coordinator.
 Logged in as Grace Lim (grace.lim@connectsphere.com / password123).</t>
         </is>
       </c>
@@ -4421,7 +4338,7 @@
       </c>
       <c r="B6" s="13" t="inlineStr">
         <is>
-          <t>The 'Assign' button is disabled, or a validation message asking to choose a coordinator is shown.
+          <t>The 'Assign' button stays disabled while 'Choose a coordinator' is selected.
 The event stays in the 'Awaiting assignment' list with status Submitted.</t>
         </is>
       </c>
@@ -4535,7 +4452,7 @@
         </is>
       </c>
     </row>
-    <row r="3" ht="58" customHeight="1">
+    <row r="3" ht="85" customHeight="1">
       <c r="A3" s="12" t="inlineStr">
         <is>
           <t>Pre-conditions</t>
@@ -4543,7 +4460,8 @@
       </c>
       <c r="B3" s="13" t="inlineStr">
         <is>
-          <t>SPM-30 fixtures loaded: 'SPM30 Meridian Graduate Evening' is Submitted with no coordinator.
+          <t>Test data loaded: run `npm run fixtures:spm30` from the project folder if it has not been run for this test pass.
+'SPM30 Meridian Graduate Evening' is Submitted with no coordinator.
 Logged in as James Koh (james.koh@meridianfina.com / password123), the event's organiser.</t>
         </is>
       </c>
@@ -4556,7 +4474,7 @@
       </c>
       <c r="B4" s="13" t="inlineStr">
         <is>
-          <t>1. Click 'All Events'
+          <t>1. Click 'My Events' in the sidebar
 2. Open 'SPM30 Meridian Graduate Evening'</t>
         </is>
       </c>
@@ -4694,7 +4612,7 @@
         </is>
       </c>
     </row>
-    <row r="3" ht="58" customHeight="1">
+    <row r="3" ht="85" customHeight="1">
       <c r="A3" s="12" t="inlineStr">
         <is>
           <t>Pre-conditions</t>
@@ -4702,7 +4620,8 @@
       </c>
       <c r="B3" s="13" t="inlineStr">
         <is>
-          <t>SPM-30 fixtures loaded: 'SPM30 Meridian Graduate Evening' is Submitted with no coordinator.
+          <t>Test data loaded: run `npm run fixtures:spm30` from the project folder if it has not been run for this test pass.
+'SPM30 Meridian Graduate Evening' is Submitted with no coordinator.
 Logged in as Daniel Tan (daniel.tan@connectsphere.com / password123), Event Coordinator.</t>
         </is>
       </c>
@@ -4734,7 +4653,7 @@
         </is>
       </c>
     </row>
-    <row r="6" ht="85" customHeight="1">
+    <row r="6" ht="98.5" customHeight="1">
       <c r="A6" s="12" t="inlineStr">
         <is>
           <t>Expected Result</t>
@@ -4744,7 +4663,7 @@
         <is>
           <t>The event does not appear under 'Awaiting your review' on Daniel Tan's dashboard.
 The event details can be viewed and show Coordinator 'Not yet assigned'.
-No options to add or edit equipment requirements, or to change the event's status, are available.</t>
+The Equipment tab shows 'Only the coordinator assigned to this event can view and manage its equipment requirements.' and no options to add or edit equipment.</t>
         </is>
       </c>
     </row>

--- a/docs/test-cases/SPM-30_Test_Cases.xlsx
+++ b/docs/test-cases/SPM-30_Test_Cases.xlsx
@@ -36,7 +36,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd"/>
   </numFmts>
-  <fonts count="7">
+  <fonts count="8">
     <font>
       <name val="Arial"/>
       <color rgb="FF000000"/>
@@ -67,6 +67,9 @@
     </font>
     <font>
       <name val="Arial"/>
+      <color rgb="FF000000"/>
+    </font>
+    <font>
       <color rgb="FF000000"/>
     </font>
   </fonts>
@@ -164,7 +167,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="33">
+  <cellXfs count="34">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="bottom"/>
     </xf>
@@ -238,6 +241,9 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -530,12 +536,12 @@
   </cols>
   <sheetData>
     <row r="1" ht="30.75" customHeight="1" s="28">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" s="31" t="inlineStr">
         <is>
           <t>Story</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" s="31" t="inlineStr">
         <is>
           <t>SPM-30: As an Event Operations Manager, I want to assign an Event Coordinator to an event so that there is a clear person responsible for coordinating it</t>
         </is>
@@ -547,32 +553,32 @@
     </row>
     <row r="2"/>
     <row r="3">
-      <c r="A3" s="1" t="inlineStr">
+      <c r="A3" s="31" t="inlineStr">
         <is>
           <t>Sheet</t>
         </is>
       </c>
-      <c r="B3" s="1" t="inlineStr">
+      <c r="B3" s="31" t="inlineStr">
         <is>
           <t>Test Case ID</t>
         </is>
       </c>
-      <c r="C3" s="1" t="inlineStr">
+      <c r="C3" s="31" t="inlineStr">
         <is>
           <t>Title</t>
         </is>
       </c>
-      <c r="D3" s="1" t="inlineStr">
+      <c r="D3" s="31" t="inlineStr">
         <is>
           <t>Linked AC</t>
         </is>
       </c>
-      <c r="E3" s="1" t="inlineStr">
+      <c r="E3" s="31" t="inlineStr">
         <is>
           <t>Type</t>
         </is>
       </c>
-      <c r="F3" s="1" t="inlineStr">
+      <c r="F3" s="31" t="inlineStr">
         <is>
           <t>Source</t>
         </is>
@@ -599,38 +605,42 @@
           <t>TC01</t>
         </is>
       </c>
-      <c r="B4" s="9" t="inlineStr">
+      <c r="B4" s="32" t="inlineStr">
         <is>
           <t>SPM-30-TC01</t>
         </is>
       </c>
-      <c r="C4" s="9" t="inlineStr">
+      <c r="C4" s="32" t="inlineStr">
         <is>
           <t>Assignments page lists only submitted events with no coordinator</t>
         </is>
       </c>
-      <c r="D4" s="9" t="inlineStr">
+      <c r="D4" s="32" t="inlineStr">
         <is>
           <t>AC2</t>
         </is>
       </c>
-      <c r="E4" s="9" t="inlineStr">
+      <c r="E4" s="32" t="inlineStr">
         <is>
           <t>Positive</t>
         </is>
       </c>
-      <c r="F4" s="9" t="inlineStr">
+      <c r="F4" s="32" t="inlineStr">
         <is>
           <t>Acceptance Criteria</t>
         </is>
       </c>
       <c r="G4" s="32" t="inlineStr">
         <is>
-          <t>Active</t>
+          <t>Updated</t>
         </is>
       </c>
       <c r="H4" s="32" t="n"/>
-      <c r="I4" s="32" t="n"/>
+      <c r="I4" s="32" t="inlineStr">
+        <is>
+          <t>Week 7 #5</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="10" t="inlineStr">
@@ -638,38 +648,42 @@
           <t>TC02</t>
         </is>
       </c>
-      <c r="B5" s="9" t="inlineStr">
+      <c r="B5" s="32" t="inlineStr">
         <is>
           <t>SPM-30-TC02</t>
         </is>
       </c>
-      <c r="C5" s="9" t="inlineStr">
+      <c r="C5" s="32" t="inlineStr">
         <is>
           <t>Ops Manager dashboard 'Awaiting assignment' shows unassigned submitted events</t>
         </is>
       </c>
-      <c r="D5" s="9" t="inlineStr">
+      <c r="D5" s="32" t="inlineStr">
         <is>
           <t>AC2</t>
         </is>
       </c>
-      <c r="E5" s="9" t="inlineStr">
+      <c r="E5" s="32" t="inlineStr">
         <is>
           <t>Positive</t>
         </is>
       </c>
-      <c r="F5" s="9" t="inlineStr">
+      <c r="F5" s="32" t="inlineStr">
         <is>
           <t>Code</t>
         </is>
       </c>
       <c r="G5" s="32" t="inlineStr">
         <is>
-          <t>Active</t>
+          <t>Updated</t>
         </is>
       </c>
       <c r="H5" s="32" t="n"/>
-      <c r="I5" s="32" t="n"/>
+      <c r="I5" s="32" t="inlineStr">
+        <is>
+          <t>Week 7 #5</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="10" t="inlineStr">
@@ -677,38 +691,42 @@
           <t>TC03</t>
         </is>
       </c>
-      <c r="B6" s="9" t="inlineStr">
+      <c r="B6" s="32" t="inlineStr">
         <is>
           <t>SPM-30-TC03</t>
         </is>
       </c>
-      <c r="C6" s="9" t="inlineStr">
+      <c r="C6" s="32" t="inlineStr">
         <is>
           <t>Non-Ops-Manager roles cannot open the Assignments page</t>
         </is>
       </c>
-      <c r="D6" s="9" t="inlineStr">
+      <c r="D6" s="32" t="inlineStr">
         <is>
           <t>AC1, AC2</t>
         </is>
       </c>
-      <c r="E6" s="9" t="inlineStr">
+      <c r="E6" s="32" t="inlineStr">
         <is>
           <t>Negative</t>
         </is>
       </c>
-      <c r="F6" s="9" t="inlineStr">
+      <c r="F6" s="32" t="inlineStr">
         <is>
           <t>Acceptance Criteria</t>
         </is>
       </c>
       <c r="G6" s="32" t="inlineStr">
         <is>
-          <t>Active</t>
+          <t>Updated</t>
         </is>
       </c>
       <c r="H6" s="32" t="n"/>
-      <c r="I6" s="32" t="n"/>
+      <c r="I6" s="32" t="inlineStr">
+        <is>
+          <t>Week 7 #5</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="10" t="inlineStr">
@@ -716,38 +734,42 @@
           <t>TC04</t>
         </is>
       </c>
-      <c r="B7" s="9" t="inlineStr">
+      <c r="B7" s="32" t="inlineStr">
         <is>
           <t>SPM-30-TC04</t>
         </is>
       </c>
-      <c r="C7" s="9" t="inlineStr">
+      <c r="C7" s="32" t="inlineStr">
         <is>
           <t>Coordinator dropdown only lists Event Coordinators</t>
         </is>
       </c>
-      <c r="D7" s="9" t="inlineStr">
+      <c r="D7" s="32" t="inlineStr">
         <is>
           <t>AC1</t>
         </is>
       </c>
-      <c r="E7" s="9" t="inlineStr">
+      <c r="E7" s="32" t="inlineStr">
         <is>
           <t>Negative</t>
         </is>
       </c>
-      <c r="F7" s="9" t="inlineStr">
+      <c r="F7" s="32" t="inlineStr">
         <is>
           <t>Acceptance Criteria</t>
         </is>
       </c>
       <c r="G7" s="32" t="inlineStr">
         <is>
-          <t>Active</t>
+          <t>Updated</t>
         </is>
       </c>
       <c r="H7" s="32" t="n"/>
-      <c r="I7" s="32" t="n"/>
+      <c r="I7" s="32" t="inlineStr">
+        <is>
+          <t>Week 7 #5</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="10" t="inlineStr">
@@ -755,27 +777,27 @@
           <t>TC05</t>
         </is>
       </c>
-      <c r="B8" s="9" t="inlineStr">
+      <c r="B8" s="32" t="inlineStr">
         <is>
           <t>SPM-30-TC05</t>
         </is>
       </c>
-      <c r="C8" s="9" t="inlineStr">
+      <c r="C8" s="32" t="inlineStr">
         <is>
           <t>Assign cannot be completed without choosing a coordinator</t>
         </is>
       </c>
-      <c r="D8" s="9" t="inlineStr">
+      <c r="D8" s="32" t="inlineStr">
         <is>
           <t>AC1</t>
         </is>
       </c>
-      <c r="E8" s="9" t="inlineStr">
+      <c r="E8" s="32" t="inlineStr">
         <is>
           <t>Negative</t>
         </is>
       </c>
-      <c r="F8" s="9" t="inlineStr">
+      <c r="F8" s="32" t="inlineStr">
         <is>
           <t>Acceptance Criteria</t>
         </is>
@@ -794,27 +816,27 @@
           <t>TC06</t>
         </is>
       </c>
-      <c r="B9" s="9" t="inlineStr">
+      <c r="B9" s="32" t="inlineStr">
         <is>
           <t>SPM-30-TC06</t>
         </is>
       </c>
-      <c r="C9" s="9" t="inlineStr">
+      <c r="C9" s="32" t="inlineStr">
         <is>
           <t>Organiser sees 'Not yet assigned' before a coordinator is assigned</t>
         </is>
       </c>
-      <c r="D9" s="9" t="inlineStr">
+      <c r="D9" s="32" t="inlineStr">
         <is>
           <t>AC5</t>
         </is>
       </c>
-      <c r="E9" s="9" t="inlineStr">
+      <c r="E9" s="32" t="inlineStr">
         <is>
           <t>Boundary</t>
         </is>
       </c>
-      <c r="F9" s="9" t="inlineStr">
+      <c r="F9" s="32" t="inlineStr">
         <is>
           <t>Code</t>
         </is>
@@ -833,27 +855,27 @@
           <t>TC07</t>
         </is>
       </c>
-      <c r="B10" s="9" t="inlineStr">
+      <c r="B10" s="32" t="inlineStr">
         <is>
           <t>SPM-30-TC07</t>
         </is>
       </c>
-      <c r="C10" s="9" t="inlineStr">
+      <c r="C10" s="32" t="inlineStr">
         <is>
           <t>Coordinators cannot manage an event that has no coordinator yet</t>
         </is>
       </c>
-      <c r="D10" s="9" t="inlineStr">
+      <c r="D10" s="32" t="inlineStr">
         <is>
           <t>AC4</t>
         </is>
       </c>
-      <c r="E10" s="9" t="inlineStr">
+      <c r="E10" s="32" t="inlineStr">
         <is>
           <t>Negative</t>
         </is>
       </c>
-      <c r="F10" s="9" t="inlineStr">
+      <c r="F10" s="32" t="inlineStr">
         <is>
           <t>Acceptance Criteria</t>
         </is>
@@ -872,27 +894,27 @@
           <t>TC08</t>
         </is>
       </c>
-      <c r="B11" s="9" t="inlineStr">
+      <c r="B11" s="32" t="inlineStr">
         <is>
           <t>SPM-30-TC08</t>
         </is>
       </c>
-      <c r="C11" s="9" t="inlineStr">
+      <c r="C11" s="32" t="inlineStr">
         <is>
           <t>Ops Manager assigns a coordinator; it is recorded and the event moves to Under review</t>
         </is>
       </c>
-      <c r="D11" s="9" t="inlineStr">
+      <c r="D11" s="32" t="inlineStr">
         <is>
           <t>AC1, AC2, AC3</t>
         </is>
       </c>
-      <c r="E11" s="9" t="inlineStr">
+      <c r="E11" s="32" t="inlineStr">
         <is>
           <t>Positive</t>
         </is>
       </c>
-      <c r="F11" s="9" t="inlineStr">
+      <c r="F11" s="32" t="inlineStr">
         <is>
           <t>Acceptance Criteria</t>
         </is>
@@ -911,27 +933,27 @@
           <t>TC09</t>
         </is>
       </c>
-      <c r="B12" s="9" t="inlineStr">
+      <c r="B12" s="32" t="inlineStr">
         <is>
           <t>SPM-30-TC09</t>
         </is>
       </c>
-      <c r="C12" s="9" t="inlineStr">
+      <c r="C12" s="32" t="inlineStr">
         <is>
           <t>Assigned coordinator sees and can manage the event</t>
         </is>
       </c>
-      <c r="D12" s="9" t="inlineStr">
+      <c r="D12" s="32" t="inlineStr">
         <is>
           <t>AC4</t>
         </is>
       </c>
-      <c r="E12" s="9" t="inlineStr">
+      <c r="E12" s="32" t="inlineStr">
         <is>
           <t>Positive</t>
         </is>
       </c>
-      <c r="F12" s="9" t="inlineStr">
+      <c r="F12" s="32" t="inlineStr">
         <is>
           <t>Acceptance Criteria</t>
         </is>
@@ -950,27 +972,27 @@
           <t>TC10</t>
         </is>
       </c>
-      <c r="B13" s="9" t="inlineStr">
+      <c r="B13" s="32" t="inlineStr">
         <is>
           <t>SPM-30-TC10</t>
         </is>
       </c>
-      <c r="C13" s="9" t="inlineStr">
+      <c r="C13" s="32" t="inlineStr">
         <is>
           <t>Owning organiser sees the assigned coordinator</t>
         </is>
       </c>
-      <c r="D13" s="9" t="inlineStr">
+      <c r="D13" s="32" t="inlineStr">
         <is>
           <t>AC5</t>
         </is>
       </c>
-      <c r="E13" s="9" t="inlineStr">
+      <c r="E13" s="32" t="inlineStr">
         <is>
           <t>Positive</t>
         </is>
       </c>
-      <c r="F13" s="9" t="inlineStr">
+      <c r="F13" s="32" t="inlineStr">
         <is>
           <t>Acceptance Criteria</t>
         </is>
@@ -989,27 +1011,27 @@
           <t>TC11</t>
         </is>
       </c>
-      <c r="B14" s="9" t="inlineStr">
+      <c r="B14" s="32" t="inlineStr">
         <is>
           <t>SPM-30-TC11</t>
         </is>
       </c>
-      <c r="C14" s="9" t="inlineStr">
+      <c r="C14" s="32" t="inlineStr">
         <is>
           <t>Organiser from the same company sees the assigned coordinator</t>
         </is>
       </c>
-      <c r="D14" s="9" t="inlineStr">
+      <c r="D14" s="32" t="inlineStr">
         <is>
           <t>AC5</t>
         </is>
       </c>
-      <c r="E14" s="9" t="inlineStr">
+      <c r="E14" s="32" t="inlineStr">
         <is>
           <t>Positive</t>
         </is>
       </c>
-      <c r="F14" s="9" t="inlineStr">
+      <c r="F14" s="32" t="inlineStr">
         <is>
           <t>Acceptance Criteria</t>
         </is>
@@ -1028,27 +1050,27 @@
           <t>TC12</t>
         </is>
       </c>
-      <c r="B15" s="9" t="inlineStr">
+      <c r="B15" s="32" t="inlineStr">
         <is>
           <t>SPM-30-TC12</t>
         </is>
       </c>
-      <c r="C15" s="9" t="inlineStr">
+      <c r="C15" s="32" t="inlineStr">
         <is>
           <t>Attendee does not see the assigned coordinator</t>
         </is>
       </c>
-      <c r="D15" s="9" t="inlineStr">
+      <c r="D15" s="32" t="inlineStr">
         <is>
           <t>AC5</t>
         </is>
       </c>
-      <c r="E15" s="9" t="inlineStr">
+      <c r="E15" s="32" t="inlineStr">
         <is>
           <t>Negative</t>
         </is>
       </c>
-      <c r="F15" s="9" t="inlineStr">
+      <c r="F15" s="32" t="inlineStr">
         <is>
           <t>Code</t>
         </is>
@@ -1067,27 +1089,27 @@
           <t>TC13</t>
         </is>
       </c>
-      <c r="B16" s="9" t="inlineStr">
+      <c r="B16" s="32" t="inlineStr">
         <is>
           <t>SPM-30-TC13</t>
         </is>
       </c>
-      <c r="C16" s="9" t="inlineStr">
+      <c r="C16" s="32" t="inlineStr">
         <is>
           <t>Ops Manager reassigns an event from the event page</t>
         </is>
       </c>
-      <c r="D16" s="9" t="inlineStr">
+      <c r="D16" s="32" t="inlineStr">
         <is>
           <t>AC6, AC3</t>
         </is>
       </c>
-      <c r="E16" s="9" t="inlineStr">
+      <c r="E16" s="32" t="inlineStr">
         <is>
           <t>Positive</t>
         </is>
       </c>
-      <c r="F16" s="9" t="inlineStr">
+      <c r="F16" s="32" t="inlineStr">
         <is>
           <t>Acceptance Criteria</t>
         </is>
@@ -1106,27 +1128,27 @@
           <t>TC14</t>
         </is>
       </c>
-      <c r="B17" s="9" t="inlineStr">
+      <c r="B17" s="32" t="inlineStr">
         <is>
           <t>SPM-30-TC14</t>
         </is>
       </c>
-      <c r="C17" s="9" t="inlineStr">
+      <c r="C17" s="32" t="inlineStr">
         <is>
           <t>After reassignment the previous coordinator loses access and the new one gains it</t>
         </is>
       </c>
-      <c r="D17" s="9" t="inlineStr">
+      <c r="D17" s="32" t="inlineStr">
         <is>
           <t>AC6, AC4</t>
         </is>
       </c>
-      <c r="E17" s="9" t="inlineStr">
+      <c r="E17" s="32" t="inlineStr">
         <is>
           <t>Positive</t>
         </is>
       </c>
-      <c r="F17" s="9" t="inlineStr">
+      <c r="F17" s="32" t="inlineStr">
         <is>
           <t>Acceptance Criteria</t>
         </is>
@@ -1145,38 +1167,42 @@
           <t>TC15</t>
         </is>
       </c>
-      <c r="B18" s="9" t="inlineStr">
+      <c r="B18" s="32" t="inlineStr">
         <is>
           <t>SPM-30-TC15</t>
         </is>
       </c>
-      <c r="C18" s="9" t="inlineStr">
+      <c r="C18" s="32" t="inlineStr">
         <is>
           <t>Ops Manager reassigns an event from the Assignments page</t>
         </is>
       </c>
-      <c r="D18" s="9" t="inlineStr">
+      <c r="D18" s="32" t="inlineStr">
         <is>
           <t>AC6, AC3</t>
         </is>
       </c>
-      <c r="E18" s="9" t="inlineStr">
+      <c r="E18" s="32" t="inlineStr">
         <is>
           <t>Positive</t>
         </is>
       </c>
-      <c r="F18" s="9" t="inlineStr">
+      <c r="F18" s="32" t="inlineStr">
         <is>
           <t>Acceptance Criteria</t>
         </is>
       </c>
       <c r="G18" s="32" t="inlineStr">
         <is>
-          <t>Active</t>
+          <t>Updated</t>
         </is>
       </c>
       <c r="H18" s="32" t="n"/>
-      <c r="I18" s="32" t="n"/>
+      <c r="I18" s="32" t="inlineStr">
+        <is>
+          <t>Week 7 #5</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="10" t="inlineStr">
@@ -1184,27 +1210,27 @@
           <t>TC16</t>
         </is>
       </c>
-      <c r="B19" s="9" t="inlineStr">
+      <c r="B19" s="32" t="inlineStr">
         <is>
           <t>SPM-30-TC16</t>
         </is>
       </c>
-      <c r="C19" s="9" t="inlineStr">
+      <c r="C19" s="32" t="inlineStr">
         <is>
           <t>Confirmed and Postponed events can be reassigned</t>
         </is>
       </c>
-      <c r="D19" s="9" t="inlineStr">
+      <c r="D19" s="32" t="inlineStr">
         <is>
           <t>AC6</t>
         </is>
       </c>
-      <c r="E19" s="9" t="inlineStr">
+      <c r="E19" s="32" t="inlineStr">
         <is>
           <t>Boundary</t>
         </is>
       </c>
-      <c r="F19" s="9" t="inlineStr">
+      <c r="F19" s="32" t="inlineStr">
         <is>
           <t>Acceptance Criteria</t>
         </is>
@@ -1223,38 +1249,42 @@
           <t>TC17</t>
         </is>
       </c>
-      <c r="B20" s="9" t="inlineStr">
+      <c r="B20" s="32" t="inlineStr">
         <is>
           <t>SPM-30-TC17</t>
         </is>
       </c>
-      <c r="C20" s="9" t="inlineStr">
+      <c r="C20" s="32" t="inlineStr">
         <is>
           <t>Completed, Cancelled and Rejected events cannot be reassigned</t>
         </is>
       </c>
-      <c r="D20" s="9" t="inlineStr">
+      <c r="D20" s="32" t="inlineStr">
         <is>
           <t>AC6</t>
         </is>
       </c>
-      <c r="E20" s="9" t="inlineStr">
+      <c r="E20" s="32" t="inlineStr">
         <is>
           <t>Negative</t>
         </is>
       </c>
-      <c r="F20" s="9" t="inlineStr">
+      <c r="F20" s="32" t="inlineStr">
         <is>
           <t>Acceptance Criteria</t>
         </is>
       </c>
       <c r="G20" s="32" t="inlineStr">
         <is>
-          <t>Active</t>
+          <t>Updated</t>
         </is>
       </c>
       <c r="H20" s="32" t="n"/>
-      <c r="I20" s="32" t="n"/>
+      <c r="I20" s="32" t="inlineStr">
+        <is>
+          <t>Week 7 #5</t>
+        </is>
+      </c>
     </row>
     <row r="21" ht="15.75" customHeight="1" s="28">
       <c r="A21" s="10" t="inlineStr">
@@ -1262,27 +1292,27 @@
           <t>TC18</t>
         </is>
       </c>
-      <c r="B21" s="9" t="inlineStr">
+      <c r="B21" s="32" t="inlineStr">
         <is>
           <t>SPM-30-TC18</t>
         </is>
       </c>
-      <c r="C21" s="9" t="inlineStr">
+      <c r="C21" s="32" t="inlineStr">
         <is>
           <t>Reassigning to the currently assigned coordinator is not a change</t>
         </is>
       </c>
-      <c r="D21" s="9" t="inlineStr">
+      <c r="D21" s="32" t="inlineStr">
         <is>
           <t>AC6</t>
         </is>
       </c>
-      <c r="E21" s="9" t="inlineStr">
+      <c r="E21" s="32" t="inlineStr">
         <is>
           <t>Boundary</t>
         </is>
       </c>
-      <c r="F21" s="9" t="inlineStr">
+      <c r="F21" s="32" t="inlineStr">
         <is>
           <t>Acceptance Criteria</t>
         </is>
@@ -1301,27 +1331,27 @@
           <t>TC19</t>
         </is>
       </c>
-      <c r="B22" s="9" t="inlineStr">
+      <c r="B22" s="32" t="inlineStr">
         <is>
           <t>SPM-30-TC19</t>
         </is>
       </c>
-      <c r="C22" s="9" t="inlineStr">
+      <c r="C22" s="32" t="inlineStr">
         <is>
           <t>Coordinator and organiser cannot change the assigned coordinator</t>
         </is>
       </c>
-      <c r="D22" s="9" t="inlineStr">
+      <c r="D22" s="32" t="inlineStr">
         <is>
           <t>AC1, AC6</t>
         </is>
       </c>
-      <c r="E22" s="9" t="inlineStr">
+      <c r="E22" s="32" t="inlineStr">
         <is>
           <t>Negative</t>
         </is>
       </c>
-      <c r="F22" s="9" t="inlineStr">
+      <c r="F22" s="32" t="inlineStr">
         <is>
           <t>Acceptance Criteria</t>
         </is>
@@ -1340,27 +1370,27 @@
           <t>TC20</t>
         </is>
       </c>
-      <c r="B23" s="9" t="inlineStr">
+      <c r="B23" s="32" t="inlineStr">
         <is>
           <t>SPM-30-TC20</t>
         </is>
       </c>
-      <c r="C23" s="9" t="inlineStr">
+      <c r="C23" s="32" t="inlineStr">
         <is>
           <t>Empty state when no events are awaiting assignment</t>
         </is>
       </c>
-      <c r="D23" s="9" t="inlineStr">
+      <c r="D23" s="32" t="inlineStr">
         <is>
           <t>AC2</t>
         </is>
       </c>
-      <c r="E23" s="9" t="inlineStr">
+      <c r="E23" s="32" t="inlineStr">
         <is>
           <t>Boundary</t>
         </is>
       </c>
-      <c r="F23" s="9" t="inlineStr">
+      <c r="F23" s="32" t="inlineStr">
         <is>
           <t>Acceptance Criteria</t>
         </is>
@@ -1376,19 +1406,19 @@
     <row r="24" ht="15.75" customHeight="1" s="28"/>
     <row r="25" ht="15.75" customHeight="1" s="28"/>
     <row r="26" ht="15.75" customHeight="1" s="28">
-      <c r="A26" s="1" t="inlineStr">
+      <c r="A26" s="31" t="inlineStr">
         <is>
           <t>AC</t>
         </is>
       </c>
-      <c r="B26" s="1" t="inlineStr">
+      <c r="B26" s="31" t="inlineStr">
         <is>
           <t>Acceptance Criterion</t>
         </is>
       </c>
       <c r="C26" s="29" t="n"/>
       <c r="D26" s="30" t="n"/>
-      <c r="E26" s="1" t="inlineStr">
+      <c r="E26" s="31" t="inlineStr">
         <is>
           <t>Covered by</t>
         </is>
@@ -1396,19 +1426,19 @@
       <c r="F26" s="30" t="n"/>
     </row>
     <row r="27" ht="71.25" customHeight="1" s="28">
-      <c r="A27" s="9" t="inlineStr">
+      <c r="A27" s="32" t="inlineStr">
         <is>
           <t>AC1</t>
         </is>
       </c>
-      <c r="B27" s="9" t="inlineStr">
+      <c r="B27" s="32" t="inlineStr">
         <is>
           <t>An authorised user can assign a coordinator to an event.</t>
         </is>
       </c>
       <c r="C27" s="29" t="n"/>
       <c r="D27" s="30" t="n"/>
-      <c r="E27" s="9" t="inlineStr">
+      <c r="E27" s="32" t="inlineStr">
         <is>
           <t>SPM-30-TC03
 SPM-30-TC04
@@ -1420,19 +1450,19 @@
       <c r="F27" s="30" t="n"/>
     </row>
     <row r="28" ht="71.25" customHeight="1" s="28">
-      <c r="A28" s="9" t="inlineStr">
+      <c r="A28" s="32" t="inlineStr">
         <is>
           <t>AC2</t>
         </is>
       </c>
-      <c r="B28" s="9" t="inlineStr">
+      <c r="B28" s="32" t="inlineStr">
         <is>
           <t>The Event Operations Manager can view or filter submitted events that do not yet have an assigned coordinator.</t>
         </is>
       </c>
       <c r="C28" s="29" t="n"/>
       <c r="D28" s="30" t="n"/>
-      <c r="E28" s="9" t="inlineStr">
+      <c r="E28" s="32" t="inlineStr">
         <is>
           <t>SPM-30-TC01
 SPM-30-TC02
@@ -1444,19 +1474,19 @@
       <c r="F28" s="30" t="n"/>
     </row>
     <row r="29" ht="44.25" customHeight="1" s="28">
-      <c r="A29" s="9" t="inlineStr">
+      <c r="A29" s="32" t="inlineStr">
         <is>
           <t>AC3</t>
         </is>
       </c>
-      <c r="B29" s="9" t="inlineStr">
+      <c r="B29" s="32" t="inlineStr">
         <is>
           <t>The assigned coordinator is recorded against the event.</t>
         </is>
       </c>
       <c r="C29" s="29" t="n"/>
       <c r="D29" s="30" t="n"/>
-      <c r="E29" s="9" t="inlineStr">
+      <c r="E29" s="32" t="inlineStr">
         <is>
           <t>SPM-30-TC08
 SPM-30-TC13
@@ -1466,19 +1496,19 @@
       <c r="F29" s="30" t="n"/>
     </row>
     <row r="30" ht="44.25" customHeight="1" s="28">
-      <c r="A30" s="9" t="inlineStr">
+      <c r="A30" s="32" t="inlineStr">
         <is>
           <t>AC4</t>
         </is>
       </c>
-      <c r="B30" s="9" t="inlineStr">
+      <c r="B30" s="32" t="inlineStr">
         <is>
           <t>The assigned coordinator can view and manage the event.</t>
         </is>
       </c>
       <c r="C30" s="29" t="n"/>
       <c r="D30" s="30" t="n"/>
-      <c r="E30" s="9" t="inlineStr">
+      <c r="E30" s="32" t="inlineStr">
         <is>
           <t>SPM-30-TC07
 SPM-30-TC09
@@ -1488,19 +1518,19 @@
       <c r="F30" s="30" t="n"/>
     </row>
     <row r="31" ht="57.75" customHeight="1" s="28">
-      <c r="A31" s="9" t="inlineStr">
+      <c r="A31" s="32" t="inlineStr">
         <is>
           <t>AC5</t>
         </is>
       </c>
-      <c r="B31" s="9" t="inlineStr">
+      <c r="B31" s="32" t="inlineStr">
         <is>
           <t>The Event Organiser can see the assigned coordinator where appropriate.</t>
         </is>
       </c>
       <c r="C31" s="29" t="n"/>
       <c r="D31" s="30" t="n"/>
-      <c r="E31" s="9" t="inlineStr">
+      <c r="E31" s="32" t="inlineStr">
         <is>
           <t>SPM-30-TC06
 SPM-30-TC10
@@ -1511,19 +1541,19 @@
       <c r="F31" s="30" t="n"/>
     </row>
     <row r="32" ht="98.25" customHeight="1" s="28">
-      <c r="A32" s="9" t="inlineStr">
+      <c r="A32" s="32" t="inlineStr">
         <is>
           <t>AC6</t>
         </is>
       </c>
-      <c r="B32" s="9" t="inlineStr">
+      <c r="B32" s="32" t="inlineStr">
         <is>
           <t>An event can be reassigned to another coordinator.</t>
         </is>
       </c>
       <c r="C32" s="29" t="n"/>
       <c r="D32" s="30" t="n"/>
-      <c r="E32" s="9" t="inlineStr">
+      <c r="E32" s="32" t="inlineStr">
         <is>
           <t>SPM-30-TC13
 SPM-30-TC14
@@ -1538,12 +1568,12 @@
     </row>
     <row r="33" ht="15.75" customHeight="1" s="28"/>
     <row r="34" ht="192.75" customHeight="1" s="28">
-      <c r="A34" s="1" t="inlineStr">
+      <c r="A34" s="31" t="inlineStr">
         <is>
           <t>Code reviewed</t>
         </is>
       </c>
-      <c r="B34" s="9" t="inlineStr">
+      <c r="B34" s="32" t="inlineStr">
         <is>
           <t>src/app/assignments/page.tsx
 design/mockups/AssignmentQueue.dc.html
@@ -2606,7 +2636,7 @@
           <t>Test Case ID</t>
         </is>
       </c>
-      <c r="B2" s="9" t="inlineStr">
+      <c r="B2" s="32" t="inlineStr">
         <is>
           <t>SPM-30-TC08</t>
         </is>
@@ -2618,7 +2648,7 @@
           <t>Pre-conditions</t>
         </is>
       </c>
-      <c r="B3" s="9" t="inlineStr">
+      <c r="B3" s="32" t="inlineStr">
         <is>
           <t>Test data loaded: run `npm run fixtures:spm30` from the project folder if it has not been run for this test pass.
 'SPM30 Nusantara Developer Meetup' (organiser Budi Santoso, Nusantara Tech Labs) is Submitted with no coordinator.
@@ -2633,7 +2663,7 @@
           <t>Test Steps</t>
         </is>
       </c>
-      <c r="B4" s="9" t="inlineStr">
+      <c r="B4" s="32" t="inlineStr">
         <is>
           <t>1. Click 'Assignments' in the sidebar
 2. In the 'Assign to' dropdown for 'SPM30 Nusantara Developer Meetup', choose 'Daniel Tan'
@@ -2649,7 +2679,7 @@
           <t>Test Data</t>
         </is>
       </c>
-      <c r="B5" s="9" t="inlineStr">
+      <c r="B5" s="32" t="inlineStr">
         <is>
           <t>Event: SPM30 Nusantara Developer Meetup | Coordinator: Daniel Tan</t>
         </is>
@@ -2661,7 +2691,7 @@
           <t>Expected Result</t>
         </is>
       </c>
-      <c r="B6" s="9" t="inlineStr">
+      <c r="B6" s="32" t="inlineStr">
         <is>
           <t>The message 'Daniel Tan is now the coordinator for "SPM30 Nusantara Developer Meetup". It has moved to Under review.' is shown.
 'SPM30 Nusantara Developer Meetup' disappears from the 'Awaiting assignment' list.
@@ -2675,7 +2705,7 @@
           <t>Created By</t>
         </is>
       </c>
-      <c r="B7" s="9" t="inlineStr">
+      <c r="B7" s="32" t="inlineStr">
         <is>
           <t>Kristen</t>
         </is>
@@ -2707,7 +2737,7 @@
           <t>Actual Result</t>
         </is>
       </c>
-      <c r="B11" s="9" t="inlineStr">
+      <c r="B11" s="32" t="inlineStr">
         <is>
           <t>The message 'Daniel Tan is now the coordinator for "SPM30 Nusantara Developer Meetup". It has moved to Under review.' is shown.
 'SPM30 Nusantara Developer Meetup' disappears from the 'Awaiting assignment' list.
@@ -2776,7 +2806,7 @@
           <t>Actual Result</t>
         </is>
       </c>
-      <c r="B18" s="9" t="inlineStr">
+      <c r="B18" s="32" t="inlineStr">
         <is>
           <t>The message 'Daniel Tan is now the coordinator for "SPM30 Nusantara Developer Meetup". It has moved to Under review.' is shown.
 'SPM30 Nusantara Developer Meetup' disappears from the 'Awaiting assignment' list.
@@ -2814,7 +2844,7 @@
           <t>Executed by</t>
         </is>
       </c>
-      <c r="B21" s="9" t="inlineStr">
+      <c r="B21" s="32" t="inlineStr">
         <is>
           <t>Sammi</t>
         </is>
@@ -3842,7 +3872,7 @@
           <t>Test Case ID</t>
         </is>
       </c>
-      <c r="B2" s="9" t="inlineStr">
+      <c r="B2" s="32" t="inlineStr">
         <is>
           <t>SPM-30-TC09</t>
         </is>
@@ -3854,7 +3884,7 @@
           <t>Pre-conditions</t>
         </is>
       </c>
-      <c r="B3" s="9" t="inlineStr">
+      <c r="B3" s="32" t="inlineStr">
         <is>
           <t>TC08 completed: Daniel Tan is assigned to 'SPM30 Nusantara Developer Meetup'.
 Logged in as Daniel Tan (daniel.tan@connectsphere.com / password123).
@@ -3868,7 +3898,7 @@
           <t>Test Steps</t>
         </is>
       </c>
-      <c r="B4" s="9" t="inlineStr">
+      <c r="B4" s="32" t="inlineStr">
         <is>
           <t>1. Open the Dashboard
 2. Open 'SPM30 Nusantara Developer Meetup' from the 'Awaiting your review' list
@@ -3883,7 +3913,7 @@
           <t>Test Data</t>
         </is>
       </c>
-      <c r="B5" s="9" t="inlineStr">
+      <c r="B5" s="32" t="inlineStr">
         <is>
           <t>Event: SPM30 Nusantara Developer Meetup | Equipment: Projector x 2</t>
         </is>
@@ -3895,7 +3925,7 @@
           <t>Expected Result</t>
         </is>
       </c>
-      <c r="B6" s="9" t="inlineStr">
+      <c r="B6" s="32" t="inlineStr">
         <is>
           <t>'SPM30 Nusantara Developer Meetup' appears under 'Awaiting your review' on Daniel Tan's dashboard.
 The equipment requirement is saved and shown in the list (management actions are available, not read-only).</t>
@@ -3908,7 +3938,7 @@
           <t>Created By</t>
         </is>
       </c>
-      <c r="B7" s="9" t="inlineStr">
+      <c r="B7" s="32" t="inlineStr">
         <is>
           <t>Kristen</t>
         </is>
@@ -3940,7 +3970,7 @@
           <t>Actual Result</t>
         </is>
       </c>
-      <c r="B11" s="9" t="inlineStr">
+      <c r="B11" s="32" t="inlineStr">
         <is>
           <t>'SPM30 Nusantara Developer Meetup' appears under 'Awaiting your review' on Daniel Tan's dashboard.
 The equipment requirement is saved and shown in the list (management actions are available, not read-only).</t>
@@ -4008,7 +4038,7 @@
           <t>Actual Result</t>
         </is>
       </c>
-      <c r="B18" s="9" t="inlineStr">
+      <c r="B18" s="32" t="inlineStr">
         <is>
           <t>'SPM30 Nusantara Developer Meetup' appears under 'Awaiting your review' on Daniel Tan's dashboard.
 The equipment requirement is saved and shown in the list (management actions are available, not read-only).</t>
@@ -4045,7 +4075,7 @@
           <t>Executed by</t>
         </is>
       </c>
-      <c r="B21" s="9" t="inlineStr">
+      <c r="B21" s="32" t="inlineStr">
         <is>
           <t>Sammi</t>
         </is>
@@ -5073,7 +5103,7 @@
           <t>Test Case ID</t>
         </is>
       </c>
-      <c r="B2" s="9" t="inlineStr">
+      <c r="B2" s="32" t="inlineStr">
         <is>
           <t>SPM-30-TC10</t>
         </is>
@@ -5085,7 +5115,7 @@
           <t>Pre-conditions</t>
         </is>
       </c>
-      <c r="B3" s="9" t="inlineStr">
+      <c r="B3" s="32" t="inlineStr">
         <is>
           <t>TC08 completed: Daniel Tan is assigned to 'SPM30 Nusantara Developer Meetup'.
 Logged in as Budi Santoso (budi.santoso@nusantaratec.com / password123), the event's organiser.
@@ -5099,7 +5129,7 @@
           <t>Test Steps</t>
         </is>
       </c>
-      <c r="B4" s="9" t="inlineStr">
+      <c r="B4" s="32" t="inlineStr">
         <is>
           <t>1. Click 'My Events' in the sidebar
 2. Open 'SPM30 Nusantara Developer Meetup'</t>
@@ -5112,7 +5142,7 @@
           <t>Test Data</t>
         </is>
       </c>
-      <c r="B5" s="9" t="inlineStr">
+      <c r="B5" s="32" t="inlineStr">
         <is>
           <t>Event: SPM30 Nusantara Developer Meetup | Organiser: Budi Santoso</t>
         </is>
@@ -5124,7 +5154,7 @@
           <t>Expected Result</t>
         </is>
       </c>
-      <c r="B6" s="9" t="inlineStr">
+      <c r="B6" s="32" t="inlineStr">
         <is>
           <t>The 'Details' card shows Coordinator 'Daniel Tan'.</t>
         </is>
@@ -5136,7 +5166,7 @@
           <t>Created By</t>
         </is>
       </c>
-      <c r="B7" s="9" t="inlineStr">
+      <c r="B7" s="32" t="inlineStr">
         <is>
           <t>Kristen</t>
         </is>
@@ -5168,7 +5198,7 @@
           <t>Actual Result</t>
         </is>
       </c>
-      <c r="B11" s="9" t="inlineStr">
+      <c r="B11" s="32" t="inlineStr">
         <is>
           <t>The 'Details' card shows Coordinator 'Daniel Tan'.</t>
         </is>
@@ -5235,7 +5265,7 @@
           <t>Actual Result</t>
         </is>
       </c>
-      <c r="B18" s="9" t="inlineStr">
+      <c r="B18" s="32" t="inlineStr">
         <is>
           <t>The 'Details' card shows Coordinator 'Daniel Tan'.</t>
         </is>
@@ -5271,7 +5301,7 @@
           <t>Executed by</t>
         </is>
       </c>
-      <c r="B21" s="9" t="inlineStr">
+      <c r="B21" s="32" t="inlineStr">
         <is>
           <t>Sammi</t>
         </is>
@@ -6299,7 +6329,7 @@
           <t>Test Case ID</t>
         </is>
       </c>
-      <c r="B2" s="9" t="inlineStr">
+      <c r="B2" s="32" t="inlineStr">
         <is>
           <t>SPM-30-TC11</t>
         </is>
@@ -6311,7 +6341,7 @@
           <t>Pre-conditions</t>
         </is>
       </c>
-      <c r="B3" s="9" t="inlineStr">
+      <c r="B3" s="32" t="inlineStr">
         <is>
           <t>Test data loaded: run `npm run fixtures:spm30` from the project folder if it has not been run for this test pass.
 'SPM30 Meridian Client Forum' (owned by James Koh, Meridian Financial Group) is Confirmed with coordinator Daniel Tan.
@@ -6325,7 +6355,7 @@
           <t>Test Steps</t>
         </is>
       </c>
-      <c r="B4" s="9" t="inlineStr">
+      <c r="B4" s="32" t="inlineStr">
         <is>
           <t>1. Click 'My Events' in the sidebar
 2. Open 'SPM30 Meridian Client Forum'</t>
@@ -6338,7 +6368,7 @@
           <t>Test Data</t>
         </is>
       </c>
-      <c r="B5" s="9" t="inlineStr">
+      <c r="B5" s="32" t="inlineStr">
         <is>
           <t>Event: SPM30 Meridian Client Forum | Viewer: Rachel Ng (same company, not owner)</t>
         </is>
@@ -6350,7 +6380,7 @@
           <t>Expected Result</t>
         </is>
       </c>
-      <c r="B6" s="9" t="inlineStr">
+      <c r="B6" s="32" t="inlineStr">
         <is>
           <t>The 'Details' card shows Coordinator 'Daniel Tan'.</t>
         </is>
@@ -6362,7 +6392,7 @@
           <t>Created By</t>
         </is>
       </c>
-      <c r="B7" s="9" t="inlineStr">
+      <c r="B7" s="32" t="inlineStr">
         <is>
           <t>Kristen</t>
         </is>
@@ -6394,7 +6424,7 @@
           <t>Actual Result</t>
         </is>
       </c>
-      <c r="B11" s="9" t="inlineStr">
+      <c r="B11" s="32" t="inlineStr">
         <is>
           <t>The 'Details' card shows Coordinator 'Daniel Tan'.</t>
         </is>
@@ -6461,7 +6491,7 @@
           <t>Actual Result</t>
         </is>
       </c>
-      <c r="B18" s="9" t="inlineStr">
+      <c r="B18" s="32" t="inlineStr">
         <is>
           <t>The 'Details' card shows Coordinator 'Daniel Tan'.</t>
         </is>
@@ -6497,7 +6527,7 @@
           <t>Executed by</t>
         </is>
       </c>
-      <c r="B21" s="9" t="inlineStr">
+      <c r="B21" s="32" t="inlineStr">
         <is>
           <t>Sammi</t>
         </is>
@@ -7525,7 +7555,7 @@
           <t>Test Case ID</t>
         </is>
       </c>
-      <c r="B2" s="9" t="inlineStr">
+      <c r="B2" s="32" t="inlineStr">
         <is>
           <t>SPM-30-TC12</t>
         </is>
@@ -7537,7 +7567,7 @@
           <t>Pre-conditions</t>
         </is>
       </c>
-      <c r="B3" s="9" t="inlineStr">
+      <c r="B3" s="32" t="inlineStr">
         <is>
           <t>Test data loaded: run `npm run fixtures:spm30` from the project folder if it has not been run for this test pass.
 'SPM30 Meridian Client Forum' is Confirmed, registration enabled, coordinator Daniel Tan.
@@ -7551,7 +7581,7 @@
           <t>Test Steps</t>
         </is>
       </c>
-      <c r="B4" s="9" t="inlineStr">
+      <c r="B4" s="32" t="inlineStr">
         <is>
           <t>1. Open 'SPM30 Meridian Client Forum' from the browse events page</t>
         </is>
@@ -7563,7 +7593,7 @@
           <t>Test Data</t>
         </is>
       </c>
-      <c r="B5" s="9" t="inlineStr">
+      <c r="B5" s="32" t="inlineStr">
         <is>
           <t>Event: SPM30 Meridian Client Forum | Viewer role: Attendee</t>
         </is>
@@ -7575,7 +7605,7 @@
           <t>Expected Result</t>
         </is>
       </c>
-      <c r="B6" s="9" t="inlineStr">
+      <c r="B6" s="32" t="inlineStr">
         <is>
           <t>The event page shows its public details only.
 No 'Coordinator' row is shown, and the name 'Daniel Tan' does not appear anywhere on the page.</t>
@@ -7588,7 +7618,7 @@
           <t>Created By</t>
         </is>
       </c>
-      <c r="B7" s="9" t="inlineStr">
+      <c r="B7" s="32" t="inlineStr">
         <is>
           <t>Kristen</t>
         </is>
@@ -7620,7 +7650,7 @@
           <t>Actual Result</t>
         </is>
       </c>
-      <c r="B11" s="9" t="inlineStr">
+      <c r="B11" s="32" t="inlineStr">
         <is>
           <t>The event page shows its public details only.
 No 'Coordinator' row is shown, and the name 'Daniel Tan' does not appear anywhere on the page.</t>
@@ -7688,7 +7718,7 @@
           <t>Actual Result</t>
         </is>
       </c>
-      <c r="B18" s="9" t="inlineStr">
+      <c r="B18" s="32" t="inlineStr">
         <is>
           <t>The event page shows its public details only.
 No 'Coordinator' row is shown, and the name 'Daniel Tan' does not appear anywhere on the page.</t>
@@ -7725,7 +7755,7 @@
           <t>Executed by</t>
         </is>
       </c>
-      <c r="B21" s="9" t="inlineStr">
+      <c r="B21" s="32" t="inlineStr">
         <is>
           <t>Sammi</t>
         </is>
@@ -8753,7 +8783,7 @@
           <t>Test Case ID</t>
         </is>
       </c>
-      <c r="B2" s="9" t="inlineStr">
+      <c r="B2" s="32" t="inlineStr">
         <is>
           <t>SPM-30-TC13</t>
         </is>
@@ -8765,7 +8795,7 @@
           <t>Pre-conditions</t>
         </is>
       </c>
-      <c r="B3" s="9" t="inlineStr">
+      <c r="B3" s="32" t="inlineStr">
         <is>
           <t>Test data loaded: run `npm run fixtures:spm30` from the project folder if it has not been run for this test pass.
 'SPM30 Kirana Regional Offsite' (organiser Faridah Aziz) is Under review with coordinator Priya Raj.
@@ -8780,7 +8810,7 @@
           <t>Test Steps</t>
         </is>
       </c>
-      <c r="B4" s="9" t="inlineStr">
+      <c r="B4" s="32" t="inlineStr">
         <is>
           <t>1. Click 'All Events'
 2. Open 'SPM30 Kirana Regional Offsite'
@@ -8797,7 +8827,7 @@
           <t>Test Data</t>
         </is>
       </c>
-      <c r="B5" s="9" t="inlineStr">
+      <c r="B5" s="32" t="inlineStr">
         <is>
           <t>Event: SPM30 Kirana Regional Offsite | From: Priya Raj | To: Joel Fernandez</t>
         </is>
@@ -8809,7 +8839,7 @@
           <t>Expected Result</t>
         </is>
       </c>
-      <c r="B6" s="9" t="inlineStr">
+      <c r="B6" s="32" t="inlineStr">
         <is>
           <t>The confirmation says the event moves from Priya Raj to Joel Fernandez.
 The message 'Reassigned from Priya Raj to Joel Fernandez.' is shown.
@@ -8824,7 +8854,7 @@
           <t>Created By</t>
         </is>
       </c>
-      <c r="B7" s="9" t="inlineStr">
+      <c r="B7" s="32" t="inlineStr">
         <is>
           <t>Kristen</t>
         </is>
@@ -8856,7 +8886,7 @@
           <t>Actual Result</t>
         </is>
       </c>
-      <c r="B11" s="9" t="inlineStr">
+      <c r="B11" s="32" t="inlineStr">
         <is>
           <t>The confirmation says the event moves from Priya Raj to Joel Fernandez.
 The message 'Reassigned from Priya Raj to Joel Fernandez.' is shown.
@@ -8926,7 +8956,7 @@
           <t>Actual Result</t>
         </is>
       </c>
-      <c r="B18" s="9" t="inlineStr">
+      <c r="B18" s="32" t="inlineStr">
         <is>
           <t>The confirmation says the event moves from Priya Raj to Joel Fernandez.
 The message 'Reassigned from Priya Raj to Joel Fernandez.' is shown.
@@ -8965,7 +8995,7 @@
           <t>Executed by</t>
         </is>
       </c>
-      <c r="B21" s="9" t="inlineStr">
+      <c r="B21" s="32" t="inlineStr">
         <is>
           <t>Sammi</t>
         </is>
@@ -9993,7 +10023,7 @@
           <t>Test Case ID</t>
         </is>
       </c>
-      <c r="B2" s="9" t="inlineStr">
+      <c r="B2" s="32" t="inlineStr">
         <is>
           <t>SPM-30-TC14</t>
         </is>
@@ -10005,7 +10035,7 @@
           <t>Pre-conditions</t>
         </is>
       </c>
-      <c r="B3" s="9" t="inlineStr">
+      <c r="B3" s="32" t="inlineStr">
         <is>
           <t>TC13 completed: 'SPM30 Kirana Regional Offsite' reassigned from Priya Raj to Joel Fernandez.
 Data reset: After this case, reset the data TC13 changed: run `npm run fixtures:spm30` from the project folder.</t>
@@ -10018,7 +10048,7 @@
           <t>Test Steps</t>
         </is>
       </c>
-      <c r="B4" s="9" t="inlineStr">
+      <c r="B4" s="32" t="inlineStr">
         <is>
           <t>1. Log in as Priya Raj (priya.raj@connectsphere.com / password123)
 2. Open the Dashboard
@@ -10034,7 +10064,7 @@
           <t>Test Data</t>
         </is>
       </c>
-      <c r="B5" s="9" t="inlineStr">
+      <c r="B5" s="32" t="inlineStr">
         <is>
           <t>Event: SPM30 Kirana Regional Offsite | Previous: Priya Raj | New: Joel Fernandez</t>
         </is>
@@ -10046,7 +10076,7 @@
           <t>Expected Result</t>
         </is>
       </c>
-      <c r="B6" s="9" t="inlineStr">
+      <c r="B6" s="32" t="inlineStr">
         <is>
           <t>The event is no longer listed on Priya Raj's dashboard, and she sees no add/edit options on its Equipment tab.
 The event is listed under 'Awaiting your review' on Joel Fernandez's dashboard.</t>
@@ -10059,7 +10089,7 @@
           <t>Created By</t>
         </is>
       </c>
-      <c r="B7" s="9" t="inlineStr">
+      <c r="B7" s="32" t="inlineStr">
         <is>
           <t>Kristen</t>
         </is>
@@ -10091,7 +10121,7 @@
           <t>Actual Result</t>
         </is>
       </c>
-      <c r="B11" s="9" t="inlineStr">
+      <c r="B11" s="32" t="inlineStr">
         <is>
           <t>The event is no longer listed on Priya Raj's dashboard, and she sees no add/edit options on its Equipment tab.
 The event is listed under 'Awaiting your review' on Joel Fernandez's dashboard.</t>
@@ -10159,7 +10189,7 @@
           <t>Actual Result</t>
         </is>
       </c>
-      <c r="B18" s="9" t="inlineStr">
+      <c r="B18" s="32" t="inlineStr">
         <is>
           <t>The event is no longer listed on Priya Raj's dashboard, and she sees no add/edit options on its Equipment tab.
 The event is listed under 'Awaiting your review' on Joel Fernandez's dashboard.</t>
@@ -10196,7 +10226,7 @@
           <t>Executed by</t>
         </is>
       </c>
-      <c r="B21" s="9" t="inlineStr">
+      <c r="B21" s="32" t="inlineStr">
         <is>
           <t>Sammi</t>
         </is>
@@ -11202,7 +11232,7 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C22"/>
+  <dimension ref="A1:C23"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="12.63" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col width="24.75" customWidth="1" style="28" min="1" max="1"/>
@@ -11210,33 +11240,40 @@
     <col width="12.63" customWidth="1" style="28" min="3" max="6"/>
   </cols>
   <sheetData>
-    <row r="1" ht="15.75" customHeight="1" s="28">
-      <c r="A1" s="2" t="inlineStr">
+    <row r="1" ht="90" customHeight="1" s="28">
+      <c r="A1" s="33" t="inlineStr">
+        <is>
+          <t>v2 (2026-10-20): The Event Operations Manager is now shown as the 'Event Coordinator Lead' (SPM-84 AC1, forum #129, Week 7 Change #5) - the same role, accounts, permissions and pages. Read 'Operations Manager', 'Event Operations Manager' or 'Ops Manager' in this case as 'Event Coordinator Lead'; on screen the role is shown under its new name, and refusals say 'Assigning coordinators is the Event Coordinator Lead's role.' On the Assignments page, SPM-30's 'Assigned' tab is now 'Active events' (SPM-84 AC5): it also lists active events with no coordinator yet, under 'Not yet assigned'.</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="17.25" customHeight="1" s="28">
+      <c r="A2" s="2" t="inlineStr">
         <is>
           <t>Item</t>
         </is>
       </c>
-      <c r="B1" s="5" t="n"/>
-    </row>
-    <row r="2" ht="17.25" customHeight="1" s="28">
-      <c r="A2" s="7" t="inlineStr">
-        <is>
-          <t>Test Case ID</t>
-        </is>
-      </c>
-      <c r="B2" s="9" t="inlineStr">
-        <is>
-          <t>SPM-30-TC15</t>
-        </is>
-      </c>
+      <c r="B2" s="5" t="n"/>
     </row>
     <row r="3" ht="125.25" customHeight="1" s="28">
       <c r="A3" s="7" t="inlineStr">
         <is>
+          <t>Test Case ID</t>
+        </is>
+      </c>
+      <c r="B3" s="32" t="inlineStr">
+        <is>
+          <t>SPM-30-TC15</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="125.25" customHeight="1" s="28">
+      <c r="A4" s="7" t="inlineStr">
+        <is>
           <t>Pre-conditions</t>
         </is>
       </c>
-      <c r="B3" s="9" t="inlineStr">
+      <c r="B4" s="32" t="inlineStr">
         <is>
           <t>Test data loaded: run `npm run fixtures:spm30` from the project folder if it has not been run for this test pass.
 'SPM30 Nusantara Product Launch' (organiser Sari Widodo) is Under review with coordinator Daniel Tan.
@@ -11245,13 +11282,13 @@
         </is>
       </c>
     </row>
-    <row r="4" ht="125.25" customHeight="1" s="28">
-      <c r="A4" s="7" t="inlineStr">
+    <row r="5" ht="30.75" customHeight="1" s="28">
+      <c r="A5" s="7" t="inlineStr">
         <is>
           <t>Test Steps</t>
         </is>
       </c>
-      <c r="B4" s="9" t="inlineStr">
+      <c r="B5" s="32" t="inlineStr">
         <is>
           <t>1. Click 'Assignments' in the sidebar
 2. Click the 'Assigned' tab
@@ -11263,25 +11300,25 @@
         </is>
       </c>
     </row>
-    <row r="5" ht="30.75" customHeight="1" s="28">
-      <c r="A5" s="7" t="inlineStr">
-        <is>
-          <t>Test Data</t>
-        </is>
-      </c>
-      <c r="B5" s="9" t="inlineStr">
-        <is>
-          <t>Event: SPM30 Nusantara Product Launch | From: Daniel Tan | To: Hui Shan Neo</t>
-        </is>
-      </c>
-    </row>
     <row r="6" ht="57.75" customHeight="1" s="28">
       <c r="A6" s="7" t="inlineStr">
         <is>
+          <t>Test Data</t>
+        </is>
+      </c>
+      <c r="B6" s="32" t="inlineStr">
+        <is>
+          <t>Event: SPM30 Nusantara Product Launch | From: Daniel Tan | To: Hui Shan Neo</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="17.25" customHeight="1" s="28">
+      <c r="A7" s="7" t="inlineStr">
+        <is>
           <t>Expected Result</t>
         </is>
       </c>
-      <c r="B6" s="9" t="inlineStr">
+      <c r="B7" s="32" t="inlineStr">
         <is>
           <t>The message '"SPM30 Nusantara Product Launch" has been reassigned from Daniel Tan to Hui Shan Neo.' is shown.
 The event page shows Coordinator 'Hui Shan Neo'.
@@ -11289,45 +11326,45 @@
         </is>
       </c>
     </row>
-    <row r="7" ht="17.25" customHeight="1" s="28">
-      <c r="A7" s="7" t="inlineStr">
-        <is>
-          <t>Created By</t>
-        </is>
-      </c>
-      <c r="B7" s="9" t="inlineStr">
-        <is>
-          <t>Kristen</t>
-        </is>
-      </c>
-    </row>
     <row r="8" ht="15.75" customHeight="1" s="28">
       <c r="A8" s="7" t="inlineStr">
         <is>
+          <t>Created By</t>
+        </is>
+      </c>
+      <c r="B8" s="32" t="inlineStr">
+        <is>
+          <t>Kristen</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="15.75" customHeight="1" s="28">
+      <c r="A9" s="7" t="inlineStr">
+        <is>
           <t>Creation Date</t>
         </is>
       </c>
-      <c r="B8" s="17" t="n">
+      <c r="B9" s="17" t="n">
         <v>46293</v>
       </c>
     </row>
-    <row r="9" ht="15.75" customHeight="1" s="28"/>
-    <row r="10" ht="15.75" customHeight="1" s="28">
-      <c r="A10" s="12" t="inlineStr">
+    <row r="10" ht="15.75" customHeight="1" s="28"/>
+    <row r="11" ht="15.75" customHeight="1" s="28">
+      <c r="A11" s="12" t="inlineStr">
         <is>
           <t>Item</t>
         </is>
       </c>
-      <c r="B10" s="13" t="n"/>
-      <c r="C10" s="14" t="n"/>
-    </row>
-    <row r="11" ht="15.75" customHeight="1" s="28">
-      <c r="A11" s="16" t="inlineStr">
+      <c r="B11" s="13" t="n"/>
+      <c r="C11" s="14" t="n"/>
+    </row>
+    <row r="12" ht="15.75" customHeight="1" s="28">
+      <c r="A12" s="16" t="inlineStr">
         <is>
           <t>Actual Result</t>
         </is>
       </c>
-      <c r="B11" s="9" t="inlineStr">
+      <c r="B12" s="32" t="inlineStr">
         <is>
           <t>The message '"SPM30 Nusantara Product Launch" has been reassigned from Daniel Tan to Hui Shan Neo.' is shown.
 The event page shows Coordinator 'Hui Shan Neo'.
@@ -11335,68 +11372,68 @@
         </is>
       </c>
     </row>
-    <row r="12" ht="15.75" customHeight="1" s="28">
-      <c r="A12" s="16" t="inlineStr">
-        <is>
-          <t>Pass/Fail/Not Executed/Blocked</t>
-        </is>
-      </c>
-      <c r="B12" s="19" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-    </row>
     <row r="13" ht="15.75" customHeight="1" s="28">
       <c r="A13" s="16" t="inlineStr">
         <is>
-          <t>Remarks</t>
-        </is>
-      </c>
-      <c r="B13" s="20" t="inlineStr">
-        <is>
-          <t>NA</t>
+          <t>Pass/Fail/Not Executed/Blocked</t>
+        </is>
+      </c>
+      <c r="B13" s="19" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
     </row>
     <row r="14" ht="15.75" customHeight="1" s="28">
       <c r="A14" s="16" t="inlineStr">
         <is>
-          <t>Executed by</t>
-        </is>
-      </c>
-      <c r="B14" s="21" t="inlineStr">
-        <is>
-          <t>Kristen</t>
+          <t>Remarks</t>
+        </is>
+      </c>
+      <c r="B14" s="20" t="inlineStr">
+        <is>
+          <t>NA</t>
         </is>
       </c>
     </row>
     <row r="15" ht="15.75" customHeight="1" s="28">
       <c r="A15" s="16" t="inlineStr">
         <is>
+          <t>Executed by</t>
+        </is>
+      </c>
+      <c r="B15" s="21" t="inlineStr">
+        <is>
+          <t>Kristen</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="15.75" customHeight="1" s="28">
+      <c r="A16" s="16" t="inlineStr">
+        <is>
           <t>Date of Execution</t>
         </is>
       </c>
-      <c r="B15" s="26" t="n">
+      <c r="B16" s="26" t="n">
         <v>46294</v>
       </c>
     </row>
-    <row r="16" ht="15.75" customHeight="1" s="28"/>
-    <row r="17" ht="15.75" customHeight="1" s="28">
-      <c r="A17" s="12" t="inlineStr">
+    <row r="17" ht="15.75" customHeight="1" s="28"/>
+    <row r="18" ht="15.75" customHeight="1" s="28">
+      <c r="A18" s="12" t="inlineStr">
         <is>
           <t>Item</t>
         </is>
       </c>
-      <c r="B17" s="13" t="n"/>
-    </row>
-    <row r="18" ht="15.75" customHeight="1" s="28">
-      <c r="A18" s="16" t="inlineStr">
+      <c r="B18" s="13" t="n"/>
+    </row>
+    <row r="19" ht="15.75" customHeight="1" s="28">
+      <c r="A19" s="16" t="inlineStr">
         <is>
           <t>Actual Result</t>
         </is>
       </c>
-      <c r="B18" s="9" t="inlineStr">
+      <c r="B19" s="32" t="inlineStr">
         <is>
           <t>The message '"SPM30 Nusantara Product Launch" has been reassigned from Daniel Tan to Hui Shan Neo.' is shown.
 The event page shows Coordinator 'Hui Shan Neo'.
@@ -11404,53 +11441,52 @@
         </is>
       </c>
     </row>
-    <row r="19" ht="15.75" customHeight="1" s="28">
-      <c r="A19" s="16" t="inlineStr">
-        <is>
-          <t>Pass/Fail/Not Executed/Blocked</t>
-        </is>
-      </c>
-      <c r="B19" s="16" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-    </row>
     <row r="20" ht="15.75" customHeight="1" s="28">
       <c r="A20" s="16" t="inlineStr">
         <is>
-          <t>Remarks</t>
+          <t>Pass/Fail/Not Executed/Blocked</t>
         </is>
       </c>
       <c r="B20" s="16" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>Pass</t>
         </is>
       </c>
     </row>
     <row r="21" ht="15.75" customHeight="1" s="28">
       <c r="A21" s="16" t="inlineStr">
         <is>
-          <t>Executed by</t>
-        </is>
-      </c>
-      <c r="B21" s="9" t="inlineStr">
-        <is>
-          <t>Sammi</t>
+          <t>Remarks</t>
+        </is>
+      </c>
+      <c r="B21" s="16" t="inlineStr">
+        <is>
+          <t>NA</t>
         </is>
       </c>
     </row>
     <row r="22" ht="15.75" customHeight="1" s="28">
       <c r="A22" s="16" t="inlineStr">
         <is>
+          <t>Executed by</t>
+        </is>
+      </c>
+      <c r="B22" s="32" t="inlineStr">
+        <is>
+          <t>Sammi</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="15.75" customHeight="1" s="28">
+      <c r="A23" s="16" t="inlineStr">
+        <is>
           <t>Date of Execution</t>
         </is>
       </c>
-      <c r="B22" s="17" t="n">
+      <c r="B23" s="17" t="n">
         <v>46295</v>
       </c>
     </row>
-    <row r="23" ht="15.75" customHeight="1" s="28"/>
     <row r="24" ht="15.75" customHeight="1" s="28"/>
     <row r="25" ht="15.75" customHeight="1" s="28"/>
     <row r="26" ht="15.75" customHeight="1" s="28"/>
@@ -12429,6 +12465,9 @@
     <row r="999" ht="15.75" customHeight="1" s="28"/>
     <row r="1000" ht="15.75" customHeight="1" s="28"/>
   </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:C1"/>
+  </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
   <pageSetup orientation="landscape"/>
 </worksheet>
@@ -12462,7 +12501,7 @@
           <t>Test Case ID</t>
         </is>
       </c>
-      <c r="B2" s="9" t="inlineStr">
+      <c r="B2" s="32" t="inlineStr">
         <is>
           <t>SPM-30-TC16</t>
         </is>
@@ -12474,7 +12513,7 @@
           <t>Pre-conditions</t>
         </is>
       </c>
-      <c r="B3" s="9" t="inlineStr">
+      <c r="B3" s="32" t="inlineStr">
         <is>
           <t>Test data loaded: run `npm run fixtures:spm30` from the project folder if it has not been run for this test pass.
 'SPM30 Anchorpoint Partner Briefing' is Confirmed with coordinator Joel Fernandez; 'SPM30 Civic Trust Workshop' is Postponed with coordinator Arif Mansor.
@@ -12489,7 +12528,7 @@
           <t>Test Steps</t>
         </is>
       </c>
-      <c r="B4" s="9" t="inlineStr">
+      <c r="B4" s="32" t="inlineStr">
         <is>
           <t>1. Click 'All Events'
 2. Open 'SPM30 Anchorpoint Partner Briefing'
@@ -12505,7 +12544,7 @@
           <t>Test Data</t>
         </is>
       </c>
-      <c r="B5" s="9" t="inlineStr">
+      <c r="B5" s="32" t="inlineStr">
         <is>
           <t>SPM30 Anchorpoint Partner Briefing (Confirmed): Joel Fernandez -&gt; Arif Mansor | SPM30 Civic Trust Workshop (Postponed): Arif Mansor -&gt; Hui Shan Neo</t>
         </is>
@@ -12517,7 +12556,7 @@
           <t>Expected Result</t>
         </is>
       </c>
-      <c r="B6" s="9" t="inlineStr">
+      <c r="B6" s="32" t="inlineStr">
         <is>
           <t>Both reassignments succeed.
 'SPM30 Anchorpoint Partner Briefing' shows Coordinator 'Arif Mansor' and stays 'Confirmed'.
@@ -12531,7 +12570,7 @@
           <t>Created By</t>
         </is>
       </c>
-      <c r="B7" s="9" t="inlineStr">
+      <c r="B7" s="32" t="inlineStr">
         <is>
           <t>Kristen</t>
         </is>
@@ -12563,7 +12602,7 @@
           <t>Actual Result</t>
         </is>
       </c>
-      <c r="B11" s="9" t="inlineStr">
+      <c r="B11" s="32" t="inlineStr">
         <is>
           <t>Both reassignments succeed.
 'SPM30 Anchorpoint Partner Briefing' shows Coordinator 'Arif Mansor' and stays 'Confirmed'.
@@ -12632,7 +12671,7 @@
           <t>Actual Result</t>
         </is>
       </c>
-      <c r="B18" s="9" t="inlineStr">
+      <c r="B18" s="32" t="inlineStr">
         <is>
           <t>Both reassignments succeed.
 'SPM30 Anchorpoint Partner Briefing' shows Coordinator 'Arif Mansor' and stays 'Confirmed'.
@@ -12670,7 +12709,7 @@
           <t>Executed by</t>
         </is>
       </c>
-      <c r="B21" s="9" t="inlineStr">
+      <c r="B21" s="32" t="inlineStr">
         <is>
           <t>Sammi</t>
         </is>
@@ -13676,7 +13715,7 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C22"/>
+  <dimension ref="A1:C23"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="12.63" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col width="24.75" customWidth="1" style="28" min="1" max="1"/>
@@ -13684,33 +13723,40 @@
     <col width="12.63" customWidth="1" style="28" min="3" max="6"/>
   </cols>
   <sheetData>
-    <row r="1" ht="15.75" customHeight="1" s="28">
-      <c r="A1" s="2" t="inlineStr">
+    <row r="1" ht="90" customHeight="1" s="28">
+      <c r="A1" s="33" t="inlineStr">
+        <is>
+          <t>v2 (2026-10-20): On the Assignments page, SPM-30's 'Assigned' tab is now 'Active events' (SPM-84 AC5): it also lists active events with no coordinator yet, under 'Not yet assigned'.</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="17.25" customHeight="1" s="28">
+      <c r="A2" s="2" t="inlineStr">
         <is>
           <t>Item</t>
         </is>
       </c>
-      <c r="B1" s="5" t="n"/>
-    </row>
-    <row r="2" ht="17.25" customHeight="1" s="28">
-      <c r="A2" s="7" t="inlineStr">
-        <is>
-          <t>Test Case ID</t>
-        </is>
-      </c>
-      <c r="B2" s="9" t="inlineStr">
-        <is>
-          <t>SPM-30-TC17</t>
-        </is>
-      </c>
+      <c r="B2" s="5" t="n"/>
     </row>
     <row r="3" ht="111.75" customHeight="1" s="28">
       <c r="A3" s="7" t="inlineStr">
         <is>
+          <t>Test Case ID</t>
+        </is>
+      </c>
+      <c r="B3" s="32" t="inlineStr">
+        <is>
+          <t>SPM-30-TC17</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="125.25" customHeight="1" s="28">
+      <c r="A4" s="7" t="inlineStr">
+        <is>
           <t>Pre-conditions</t>
         </is>
       </c>
-      <c r="B3" s="9" t="inlineStr">
+      <c r="B4" s="32" t="inlineStr">
         <is>
           <t>Test data loaded: run `npm run fixtures:spm30` from the project folder if it has not been run for this test pass.
 'SPM30 Harbourline Claims Training' is Completed (Priya Raj), 'SPM30 Pearl Delta Supplier Forum' is Cancelled (Joel Fernandez), 'SPM30 Selaras Overnight Field Day' is Rejected (Priya Raj).
@@ -13718,13 +13764,13 @@
         </is>
       </c>
     </row>
-    <row r="4" ht="125.25" customHeight="1" s="28">
-      <c r="A4" s="7" t="inlineStr">
+    <row r="5" ht="44.25" customHeight="1" s="28">
+      <c r="A5" s="7" t="inlineStr">
         <is>
           <t>Test Steps</t>
         </is>
       </c>
-      <c r="B4" s="9" t="inlineStr">
+      <c r="B5" s="32" t="inlineStr">
         <is>
           <t>1. Click 'All Events'
 2. Open 'SPM30 Harbourline Claims Training' and look for a 'Change coordinator' card
@@ -13734,25 +13780,25 @@
         </is>
       </c>
     </row>
-    <row r="5" ht="44.25" customHeight="1" s="28">
-      <c r="A5" s="7" t="inlineStr">
-        <is>
-          <t>Test Data</t>
-        </is>
-      </c>
-      <c r="B5" s="9" t="inlineStr">
-        <is>
-          <t>Events: SPM30 Harbourline Claims Training (Completed), SPM30 Pearl Delta Supplier Forum (Cancelled), SPM30 Selaras Overnight Field Day (Rejected)</t>
-        </is>
-      </c>
-    </row>
     <row r="6" ht="44.25" customHeight="1" s="28">
       <c r="A6" s="7" t="inlineStr">
         <is>
+          <t>Test Data</t>
+        </is>
+      </c>
+      <c r="B6" s="32" t="inlineStr">
+        <is>
+          <t>Events: SPM30 Harbourline Claims Training (Completed), SPM30 Pearl Delta Supplier Forum (Cancelled), SPM30 Selaras Overnight Field Day (Rejected)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="17.25" customHeight="1" s="28">
+      <c r="A7" s="7" t="inlineStr">
+        <is>
           <t>Expected Result</t>
         </is>
       </c>
-      <c r="B6" s="9" t="inlineStr">
+      <c r="B7" s="32" t="inlineStr">
         <is>
           <t>None of the three events shows a 'Change coordinator' card.
 None of them appear on either Assignments tab.
@@ -13760,45 +13806,45 @@
         </is>
       </c>
     </row>
-    <row r="7" ht="17.25" customHeight="1" s="28">
-      <c r="A7" s="7" t="inlineStr">
-        <is>
-          <t>Created By</t>
-        </is>
-      </c>
-      <c r="B7" s="9" t="inlineStr">
-        <is>
-          <t>Kristen</t>
-        </is>
-      </c>
-    </row>
     <row r="8" ht="15.75" customHeight="1" s="28">
       <c r="A8" s="7" t="inlineStr">
         <is>
+          <t>Created By</t>
+        </is>
+      </c>
+      <c r="B8" s="32" t="inlineStr">
+        <is>
+          <t>Kristen</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="15.75" customHeight="1" s="28">
+      <c r="A9" s="7" t="inlineStr">
+        <is>
           <t>Creation Date</t>
         </is>
       </c>
-      <c r="B8" s="17" t="n">
+      <c r="B9" s="17" t="n">
         <v>46293</v>
       </c>
     </row>
-    <row r="9" ht="15.75" customHeight="1" s="28"/>
-    <row r="10" ht="15.75" customHeight="1" s="28">
-      <c r="A10" s="12" t="inlineStr">
+    <row r="10" ht="15.75" customHeight="1" s="28"/>
+    <row r="11" ht="15.75" customHeight="1" s="28">
+      <c r="A11" s="12" t="inlineStr">
         <is>
           <t>Item</t>
         </is>
       </c>
-      <c r="B10" s="13" t="n"/>
-      <c r="C10" s="14" t="n"/>
-    </row>
-    <row r="11" ht="15.75" customHeight="1" s="28">
-      <c r="A11" s="16" t="inlineStr">
+      <c r="B11" s="13" t="n"/>
+      <c r="C11" s="14" t="n"/>
+    </row>
+    <row r="12" ht="15.75" customHeight="1" s="28">
+      <c r="A12" s="16" t="inlineStr">
         <is>
           <t>Actual Result</t>
         </is>
       </c>
-      <c r="B11" s="9" t="inlineStr">
+      <c r="B12" s="32" t="inlineStr">
         <is>
           <t>None of the three events shows a 'Change coordinator' card.
 None of them appear on either Assignments tab.
@@ -13806,68 +13852,68 @@
         </is>
       </c>
     </row>
-    <row r="12" ht="15.75" customHeight="1" s="28">
-      <c r="A12" s="16" t="inlineStr">
-        <is>
-          <t>Pass/Fail/Not Executed/Blocked</t>
-        </is>
-      </c>
-      <c r="B12" s="23" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-    </row>
     <row r="13" ht="15.75" customHeight="1" s="28">
       <c r="A13" s="16" t="inlineStr">
         <is>
-          <t>Remarks</t>
-        </is>
-      </c>
-      <c r="B13" s="24" t="inlineStr">
-        <is>
-          <t>NA</t>
+          <t>Pass/Fail/Not Executed/Blocked</t>
+        </is>
+      </c>
+      <c r="B13" s="23" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
     </row>
     <row r="14" ht="15.75" customHeight="1" s="28">
       <c r="A14" s="16" t="inlineStr">
         <is>
-          <t>Executed by</t>
-        </is>
-      </c>
-      <c r="B14" s="25" t="inlineStr">
-        <is>
-          <t>Kristen</t>
+          <t>Remarks</t>
+        </is>
+      </c>
+      <c r="B14" s="24" t="inlineStr">
+        <is>
+          <t>NA</t>
         </is>
       </c>
     </row>
     <row r="15" ht="15.75" customHeight="1" s="28">
       <c r="A15" s="16" t="inlineStr">
         <is>
+          <t>Executed by</t>
+        </is>
+      </c>
+      <c r="B15" s="25" t="inlineStr">
+        <is>
+          <t>Kristen</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="15.75" customHeight="1" s="28">
+      <c r="A16" s="16" t="inlineStr">
+        <is>
           <t>Date of Execution</t>
         </is>
       </c>
-      <c r="B15" s="26" t="n">
+      <c r="B16" s="26" t="n">
         <v>46294</v>
       </c>
     </row>
-    <row r="16" ht="15.75" customHeight="1" s="28"/>
-    <row r="17" ht="15.75" customHeight="1" s="28">
-      <c r="A17" s="12" t="inlineStr">
+    <row r="17" ht="15.75" customHeight="1" s="28"/>
+    <row r="18" ht="15.75" customHeight="1" s="28">
+      <c r="A18" s="12" t="inlineStr">
         <is>
           <t>Item</t>
         </is>
       </c>
-      <c r="B17" s="13" t="n"/>
-    </row>
-    <row r="18" ht="15.75" customHeight="1" s="28">
-      <c r="A18" s="16" t="inlineStr">
+      <c r="B18" s="13" t="n"/>
+    </row>
+    <row r="19" ht="15.75" customHeight="1" s="28">
+      <c r="A19" s="16" t="inlineStr">
         <is>
           <t>Actual Result</t>
         </is>
       </c>
-      <c r="B18" s="9" t="inlineStr">
+      <c r="B19" s="32" t="inlineStr">
         <is>
           <t>None of the three events shows a 'Change coordinator' card.
 None of them appear on either Assignments tab.
@@ -13875,53 +13921,52 @@
         </is>
       </c>
     </row>
-    <row r="19" ht="15.75" customHeight="1" s="28">
-      <c r="A19" s="16" t="inlineStr">
-        <is>
-          <t>Pass/Fail/Not Executed/Blocked</t>
-        </is>
-      </c>
-      <c r="B19" s="16" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-    </row>
     <row r="20" ht="15.75" customHeight="1" s="28">
       <c r="A20" s="16" t="inlineStr">
         <is>
-          <t>Remarks</t>
+          <t>Pass/Fail/Not Executed/Blocked</t>
         </is>
       </c>
       <c r="B20" s="16" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>Pass</t>
         </is>
       </c>
     </row>
     <row r="21" ht="15.75" customHeight="1" s="28">
       <c r="A21" s="16" t="inlineStr">
         <is>
-          <t>Executed by</t>
-        </is>
-      </c>
-      <c r="B21" s="9" t="inlineStr">
-        <is>
-          <t>Sammi</t>
+          <t>Remarks</t>
+        </is>
+      </c>
+      <c r="B21" s="16" t="inlineStr">
+        <is>
+          <t>NA</t>
         </is>
       </c>
     </row>
     <row r="22" ht="15.75" customHeight="1" s="28">
       <c r="A22" s="16" t="inlineStr">
         <is>
+          <t>Executed by</t>
+        </is>
+      </c>
+      <c r="B22" s="32" t="inlineStr">
+        <is>
+          <t>Sammi</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="15.75" customHeight="1" s="28">
+      <c r="A23" s="16" t="inlineStr">
+        <is>
           <t>Date of Execution</t>
         </is>
       </c>
-      <c r="B22" s="17" t="n">
+      <c r="B23" s="17" t="n">
         <v>46295</v>
       </c>
     </row>
-    <row r="23" ht="15.75" customHeight="1" s="28"/>
     <row r="24" ht="15.75" customHeight="1" s="28"/>
     <row r="25" ht="15.75" customHeight="1" s="28"/>
     <row r="26" ht="15.75" customHeight="1" s="28"/>
@@ -14900,6 +14945,9 @@
     <row r="999" ht="15.75" customHeight="1" s="28"/>
     <row r="1000" ht="15.75" customHeight="1" s="28"/>
   </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:C1"/>
+  </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
   <pageSetup orientation="landscape"/>
 </worksheet>
@@ -14921,65 +14969,65 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" s="31" t="inlineStr">
         <is>
           <t>#</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" s="31" t="inlineStr">
         <is>
           <t>Question / ambiguity for the PO or developer</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" s="31" t="inlineStr">
         <is>
           <t>Answer</t>
         </is>
       </c>
     </row>
     <row r="2" ht="57.75" customHeight="1" s="28">
-      <c r="A2" s="9" t="n">
+      <c r="A2" s="32" t="n">
         <v>1</v>
       </c>
-      <c r="B2" s="9" t="inlineStr">
+      <c r="B2" s="32" t="inlineStr">
         <is>
           <t>NOTE: Test data comes from scripts/seed-spm30.ts (npm run fixtures:spm30). It only deletes and recreates events whose seed key starts with 'spm30_'; the rest of the database is untouched. Run it before a full pass, and wherever a case's 'Data reset' line says to.</t>
         </is>
       </c>
-      <c r="C2" s="9" t="n"/>
+      <c r="C2" s="32" t="n"/>
     </row>
     <row r="3" ht="57.75" customHeight="1" s="28">
-      <c r="A3" s="9" t="n">
+      <c r="A3" s="32" t="n">
         <v>2</v>
       </c>
-      <c r="B3" s="9" t="inlineStr">
+      <c r="B3" s="32" t="inlineStr">
         <is>
           <t>NOTE: TC20 (empty state) needs zero unassigned submitted events in the whole database, which on the shared database means assigning base-seed events such as 'Nusantara Developer Summit'. The fixture script does not restore those. Run TC20 on a Neon branch or local database.</t>
         </is>
       </c>
-      <c r="C3" s="9" t="n"/>
+      <c r="C3" s="32" t="n"/>
     </row>
     <row r="4" ht="30.75" customHeight="1" s="28">
-      <c r="A4" s="9" t="n">
+      <c r="A4" s="32" t="n">
         <v>3</v>
       </c>
-      <c r="B4" s="9" t="inlineStr">
+      <c r="B4" s="32" t="inlineStr">
         <is>
           <t>NOTE: Organisers from an unrelated company not seeing the event is covered by SPM-31 (visibility), so it is not repeated here.</t>
         </is>
       </c>
-      <c r="C4" s="9" t="n"/>
+      <c r="C4" s="32" t="n"/>
     </row>
     <row r="5" ht="57.75" customHeight="1" s="28">
-      <c r="A5" s="9" t="n">
+      <c r="A5" s="32" t="n">
         <v>4</v>
       </c>
-      <c r="B5" s="9" t="inlineStr">
+      <c r="B5" s="32" t="inlineStr">
         <is>
           <t>OPEN: Notifications are written on assignment (new coordinator) and reassignment (new and previous coordinator), but there are no test cases for them yet because the Notifications page (S-04, SPM-53) is still a placeholder. Add them once SPM-53 is built.</t>
         </is>
       </c>
-      <c r="C5" s="9" t="n"/>
+      <c r="C5" s="32" t="n"/>
     </row>
     <row r="21" ht="15.75" customHeight="1" s="28"/>
     <row r="22" ht="15.75" customHeight="1" s="28"/>
@@ -15995,7 +16043,7 @@
           <t>Test Case ID</t>
         </is>
       </c>
-      <c r="B2" s="9" t="inlineStr">
+      <c r="B2" s="32" t="inlineStr">
         <is>
           <t>SPM-30-TC18</t>
         </is>
@@ -16007,7 +16055,7 @@
           <t>Pre-conditions</t>
         </is>
       </c>
-      <c r="B3" s="9" t="inlineStr">
+      <c r="B3" s="32" t="inlineStr">
         <is>
           <t>Test data loaded: run `npm run fixtures:spm30` from the project folder if it has not been run for this test pass.
 'SPM30 Straits Journal Club' is Under review with coordinator Joel Fernandez.
@@ -16021,7 +16069,7 @@
           <t>Test Steps</t>
         </is>
       </c>
-      <c r="B4" s="9" t="inlineStr">
+      <c r="B4" s="32" t="inlineStr">
         <is>
           <t>1. Click 'All Events'
 2. Open 'SPM30 Straits Journal Club'
@@ -16035,7 +16083,7 @@
           <t>Test Data</t>
         </is>
       </c>
-      <c r="B5" s="9" t="inlineStr">
+      <c r="B5" s="32" t="inlineStr">
         <is>
           <t>Event: SPM30 Straits Journal Club | Coordinator: Joel Fernandez -&gt; Joel Fernandez</t>
         </is>
@@ -16047,7 +16095,7 @@
           <t>Expected Result</t>
         </is>
       </c>
-      <c r="B6" s="9" t="inlineStr">
+      <c r="B6" s="32" t="inlineStr">
         <is>
           <t>The message 'Joel Fernandez is already the assigned coordinator.' appears under the dropdown.
 The 'Reassign' button stays disabled.
@@ -16061,7 +16109,7 @@
           <t>Created By</t>
         </is>
       </c>
-      <c r="B7" s="9" t="inlineStr">
+      <c r="B7" s="32" t="inlineStr">
         <is>
           <t>Kristen</t>
         </is>
@@ -16093,7 +16141,7 @@
           <t>Actual Result</t>
         </is>
       </c>
-      <c r="B11" s="9" t="inlineStr">
+      <c r="B11" s="32" t="inlineStr">
         <is>
           <t>The message 'Joel Fernandez is already the assigned coordinator.' appears under the dropdown.
 The 'Reassign' button stays disabled.
@@ -16162,7 +16210,7 @@
           <t>Actual Result</t>
         </is>
       </c>
-      <c r="B18" s="9" t="inlineStr">
+      <c r="B18" s="32" t="inlineStr">
         <is>
           <t>The message 'Joel Fernandez is already the assigned coordinator.' appears under the dropdown.
 The 'Reassign' button stays disabled.
@@ -16200,7 +16248,7 @@
           <t>Executed by</t>
         </is>
       </c>
-      <c r="B21" s="9" t="inlineStr">
+      <c r="B21" s="32" t="inlineStr">
         <is>
           <t>Sammi</t>
         </is>
@@ -17228,7 +17276,7 @@
           <t>Test Case ID</t>
         </is>
       </c>
-      <c r="B2" s="9" t="inlineStr">
+      <c r="B2" s="32" t="inlineStr">
         <is>
           <t>SPM-30-TC19</t>
         </is>
@@ -17240,7 +17288,7 @@
           <t>Pre-conditions</t>
         </is>
       </c>
-      <c r="B3" s="9" t="inlineStr">
+      <c r="B3" s="32" t="inlineStr">
         <is>
           <t>Test data loaded: run `npm run fixtures:spm30` from the project folder if it has not been run for this test pass.
 'SPM30 Straits Journal Club' is Under review with coordinator Joel Fernandez (organiser Raj Kumar).</t>
@@ -17253,7 +17301,7 @@
           <t>Test Steps</t>
         </is>
       </c>
-      <c r="B4" s="9" t="inlineStr">
+      <c r="B4" s="32" t="inlineStr">
         <is>
           <t>1. Log in as Joel Fernandez (joel.fernandez@connectsphere.com / password123)
 2. Click 'All Events', open 'SPM30 Straits Journal Club' and look for a 'Change coordinator' card
@@ -17268,7 +17316,7 @@
           <t>Test Data</t>
         </is>
       </c>
-      <c r="B5" s="9" t="inlineStr">
+      <c r="B5" s="32" t="inlineStr">
         <is>
           <t>Event: SPM30 Straits Journal Club | Roles: Event Coordinator, Event Organiser</t>
         </is>
@@ -17280,7 +17328,7 @@
           <t>Expected Result</t>
         </is>
       </c>
-      <c r="B6" s="9" t="inlineStr">
+      <c r="B6" s="32" t="inlineStr">
         <is>
           <t>Neither user sees a 'Change coordinator' card or any other way to assign or change the coordinator.
 The 'Details' card shows Coordinator 'Joel Fernandez' as read-only text.</t>
@@ -17293,7 +17341,7 @@
           <t>Created By</t>
         </is>
       </c>
-      <c r="B7" s="9" t="inlineStr">
+      <c r="B7" s="32" t="inlineStr">
         <is>
           <t>Kristen</t>
         </is>
@@ -17325,7 +17373,7 @@
           <t>Actual Result</t>
         </is>
       </c>
-      <c r="B11" s="9" t="inlineStr">
+      <c r="B11" s="32" t="inlineStr">
         <is>
           <t>Neither user sees a 'Change coordinator' card or any other way to assign or change the coordinator.
 The 'Details' card shows Coordinator 'Joel Fernandez' as read-only text.</t>
@@ -17393,7 +17441,7 @@
           <t>Actual Result</t>
         </is>
       </c>
-      <c r="B18" s="9" t="inlineStr">
+      <c r="B18" s="32" t="inlineStr">
         <is>
           <t>Neither user sees a 'Change coordinator' card or any other way to assign or change the coordinator.
 The 'Details' card shows Coordinator 'Joel Fernandez' as read-only text.</t>
@@ -17430,7 +17478,7 @@
           <t>Executed by</t>
         </is>
       </c>
-      <c r="B21" s="9" t="inlineStr">
+      <c r="B21" s="32" t="inlineStr">
         <is>
           <t>Sammi</t>
         </is>
@@ -18458,7 +18506,7 @@
           <t>Test Case ID</t>
         </is>
       </c>
-      <c r="B2" s="9" t="inlineStr">
+      <c r="B2" s="32" t="inlineStr">
         <is>
           <t>SPM-30-TC20</t>
         </is>
@@ -18525,7 +18573,7 @@
           <t>Created By</t>
         </is>
       </c>
-      <c r="B7" s="9" t="inlineStr">
+      <c r="B7" s="32" t="inlineStr">
         <is>
           <t>Kristen</t>
         </is>
@@ -18662,7 +18710,7 @@
           <t>Executed by</t>
         </is>
       </c>
-      <c r="B21" s="9" t="inlineStr">
+      <c r="B21" s="32" t="inlineStr">
         <is>
           <t>Sammi</t>
         </is>
@@ -19668,7 +19716,7 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C22"/>
+  <dimension ref="A1:C23"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="12.63" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col width="24.75" customWidth="1" style="28" min="1" max="1"/>
@@ -19676,71 +19724,78 @@
     <col width="12.63" customWidth="1" style="28" min="3" max="6"/>
   </cols>
   <sheetData>
-    <row r="1" ht="15.75" customHeight="1" s="28">
-      <c r="A1" s="2" t="inlineStr">
+    <row r="1" ht="90" customHeight="1" s="28">
+      <c r="A1" s="33" t="inlineStr">
+        <is>
+          <t>v2 (2026-10-20): The Event Operations Manager is now shown as the 'Event Coordinator Lead' (SPM-84 AC1, forum #129, Week 7 Change #5) - the same role, accounts, permissions and pages. Read 'Operations Manager', 'Event Operations Manager' or 'Ops Manager' in this case as 'Event Coordinator Lead'; on screen the role is shown under its new name, and refusals say 'Assigning coordinators is the Event Coordinator Lead's role.'</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="17.25" customHeight="1" s="28">
+      <c r="A2" s="2" t="inlineStr">
         <is>
           <t>Item</t>
         </is>
       </c>
-      <c r="B1" s="5" t="n"/>
-    </row>
-    <row r="2" ht="17.25" customHeight="1" s="28">
-      <c r="A2" s="7" t="inlineStr">
-        <is>
-          <t>Test Case ID</t>
-        </is>
-      </c>
-      <c r="B2" s="9" t="inlineStr">
-        <is>
-          <t>SPM-30-TC01</t>
-        </is>
-      </c>
+      <c r="B2" s="5" t="n"/>
     </row>
     <row r="3" ht="57.75" customHeight="1" s="28">
       <c r="A3" s="7" t="inlineStr">
         <is>
+          <t>Test Case ID</t>
+        </is>
+      </c>
+      <c r="B3" s="32" t="inlineStr">
+        <is>
+          <t>SPM-30-TC01</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="44.25" customHeight="1" s="28">
+      <c r="A4" s="7" t="inlineStr">
+        <is>
           <t>Pre-conditions</t>
         </is>
       </c>
-      <c r="B3" s="9" t="inlineStr">
+      <c r="B4" s="32" t="inlineStr">
         <is>
           <t>Test data freshly loaded: run `npm run fixtures:spm30` from the project folder just before this case.
 Logged in as Grace Lim (grace.lim@connectsphere.com / password123), Event Operations Manager.</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="44.25" customHeight="1" s="28">
-      <c r="A4" s="7" t="inlineStr">
+    <row r="5" ht="57.75" customHeight="1" s="28">
+      <c r="A5" s="7" t="inlineStr">
         <is>
           <t>Test Steps</t>
         </is>
       </c>
-      <c r="B4" s="9" t="inlineStr">
+      <c r="B5" s="32" t="inlineStr">
         <is>
           <t>1. Click 'Assignments' in the sidebar
 2. Click 'SPM30 Meridian Graduate Evening' in the list to open it</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="57.75" customHeight="1" s="28">
-      <c r="A5" s="7" t="inlineStr">
-        <is>
-          <t>Test Data</t>
-        </is>
-      </c>
-      <c r="B5" s="9" t="inlineStr">
-        <is>
-          <t>Expected rows include: SPM30 Nusantara Developer Meetup, SPM30 Meridian Graduate Evening | Must not appear: SPM30 Kirana Regional Offsite (Under review, Priya Raj), SPM30 Draft Investor Update (Draft)</t>
-        </is>
-      </c>
-    </row>
     <row r="6" ht="152.25" customHeight="1" s="28">
       <c r="A6" s="7" t="inlineStr">
         <is>
+          <t>Test Data</t>
+        </is>
+      </c>
+      <c r="B6" s="32" t="inlineStr">
+        <is>
+          <t>Expected rows include: SPM30 Nusantara Developer Meetup, SPM30 Meridian Graduate Evening | Must not appear: SPM30 Kirana Regional Offsite (Under review, Priya Raj), SPM30 Draft Investor Update (Draft)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="17.25" customHeight="1" s="28">
+      <c r="A7" s="7" t="inlineStr">
+        <is>
           <t>Expected Result</t>
         </is>
       </c>
-      <c r="B6" s="9" t="inlineStr">
+      <c r="B7" s="32" t="inlineStr">
         <is>
           <t>The 'Awaiting assignment' table shows 'SPM30 Nusantara Developer Meetup' and 'SPM30 Meridian Graduate Evening' with their client, date and how long they have been waiting. Base-seed events that are also submitted with no coordinator (e.g. 'Nusantara Developer Summit', 'Meridian Graduate Recruitment Evening') may appear too.
 'SPM30 Kirana Regional Offsite' (already has a coordinator) is not listed.
@@ -19749,45 +19804,45 @@
         </is>
       </c>
     </row>
-    <row r="7" ht="17.25" customHeight="1" s="28">
-      <c r="A7" s="7" t="inlineStr">
-        <is>
-          <t>Created By</t>
-        </is>
-      </c>
-      <c r="B7" s="9" t="inlineStr">
-        <is>
-          <t>Kristen</t>
-        </is>
-      </c>
-    </row>
     <row r="8" ht="15.75" customHeight="1" s="28">
       <c r="A8" s="7" t="inlineStr">
         <is>
+          <t>Created By</t>
+        </is>
+      </c>
+      <c r="B8" s="32" t="inlineStr">
+        <is>
+          <t>Kristen</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="15.75" customHeight="1" s="28">
+      <c r="A9" s="7" t="inlineStr">
+        <is>
           <t>Creation Date</t>
         </is>
       </c>
-      <c r="B8" s="17" t="n">
+      <c r="B9" s="17" t="n">
         <v>46293</v>
       </c>
     </row>
-    <row r="9" ht="15.75" customHeight="1" s="28"/>
-    <row r="10" ht="15.75" customHeight="1" s="28">
-      <c r="A10" s="12" t="inlineStr">
+    <row r="10" ht="15.75" customHeight="1" s="28"/>
+    <row r="11" ht="15.75" customHeight="1" s="28">
+      <c r="A11" s="12" t="inlineStr">
         <is>
           <t>Item</t>
         </is>
       </c>
-      <c r="B10" s="13" t="n"/>
-      <c r="C10" s="14" t="n"/>
-    </row>
-    <row r="11" ht="15.75" customHeight="1" s="28">
-      <c r="A11" s="16" t="inlineStr">
+      <c r="B11" s="13" t="n"/>
+      <c r="C11" s="14" t="n"/>
+    </row>
+    <row r="12" ht="15.75" customHeight="1" s="28">
+      <c r="A12" s="16" t="inlineStr">
         <is>
           <t>Actual Result</t>
         </is>
       </c>
-      <c r="B11" s="9" t="inlineStr">
+      <c r="B12" s="32" t="inlineStr">
         <is>
           <t>The 'Awaiting assignment' table shows 'SPM30 Nusantara Developer Meetup' and 'SPM30 Meridian Graduate Evening' with their client, date and how long they have been waiting. Base-seed events that are also submitted with no coordinator (e.g. 'Nusantara Developer Summit', 'Meridian Graduate Recruitment Evening') may appear too.
 'SPM30 Kirana Regional Offsite' (already has a coordinator) is not listed.
@@ -19796,68 +19851,68 @@
         </is>
       </c>
     </row>
-    <row r="12" ht="15.75" customHeight="1" s="28">
-      <c r="A12" s="16" t="inlineStr">
-        <is>
-          <t>Pass/Fail/Not Executed/Blocked</t>
-        </is>
-      </c>
-      <c r="B12" s="16" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-    </row>
     <row r="13" ht="15.75" customHeight="1" s="28">
       <c r="A13" s="16" t="inlineStr">
         <is>
-          <t>Remarks</t>
+          <t>Pass/Fail/Not Executed/Blocked</t>
         </is>
       </c>
       <c r="B13" s="16" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>Pass</t>
         </is>
       </c>
     </row>
     <row r="14" ht="15.75" customHeight="1" s="28">
       <c r="A14" s="16" t="inlineStr">
         <is>
-          <t>Executed by</t>
-        </is>
-      </c>
-      <c r="B14" s="9" t="inlineStr">
-        <is>
-          <t>Kristen</t>
+          <t>Remarks</t>
+        </is>
+      </c>
+      <c r="B14" s="16" t="inlineStr">
+        <is>
+          <t>NA</t>
         </is>
       </c>
     </row>
     <row r="15" ht="15.75" customHeight="1" s="28">
       <c r="A15" s="16" t="inlineStr">
         <is>
+          <t>Executed by</t>
+        </is>
+      </c>
+      <c r="B15" s="32" t="inlineStr">
+        <is>
+          <t>Kristen</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="15.75" customHeight="1" s="28">
+      <c r="A16" s="16" t="inlineStr">
+        <is>
           <t>Date of Execution</t>
         </is>
       </c>
-      <c r="B15" s="17" t="n">
+      <c r="B16" s="17" t="n">
         <v>46294</v>
       </c>
     </row>
-    <row r="16" ht="15.75" customHeight="1" s="28"/>
-    <row r="17" ht="15.75" customHeight="1" s="28">
-      <c r="A17" s="12" t="inlineStr">
+    <row r="17" ht="15.75" customHeight="1" s="28"/>
+    <row r="18" ht="15.75" customHeight="1" s="28">
+      <c r="A18" s="12" t="inlineStr">
         <is>
           <t>Item</t>
         </is>
       </c>
-      <c r="B17" s="13" t="n"/>
-    </row>
-    <row r="18" ht="15.75" customHeight="1" s="28">
-      <c r="A18" s="16" t="inlineStr">
+      <c r="B18" s="13" t="n"/>
+    </row>
+    <row r="19" ht="15.75" customHeight="1" s="28">
+      <c r="A19" s="16" t="inlineStr">
         <is>
           <t>Actual Result</t>
         </is>
       </c>
-      <c r="B18" s="9" t="inlineStr">
+      <c r="B19" s="32" t="inlineStr">
         <is>
           <t>The 'Awaiting assignment' table shows 'SPM30 Nusantara Developer Meetup' and 'SPM30 Meridian Graduate Evening' with their client, date and how long they have been waiting. Base-seed events that are also submitted with no coordinator (e.g. 'Nusantara Developer Summit', 'Meridian Graduate Recruitment Evening') may appear too.
 'SPM30 Kirana Regional Offsite' (already has a coordinator) is not listed.
@@ -19866,53 +19921,52 @@
         </is>
       </c>
     </row>
-    <row r="19" ht="15.75" customHeight="1" s="28">
-      <c r="A19" s="16" t="inlineStr">
-        <is>
-          <t>Pass/Fail/Not Executed/Blocked</t>
-        </is>
-      </c>
-      <c r="B19" s="16" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-    </row>
     <row r="20" ht="15.75" customHeight="1" s="28">
       <c r="A20" s="16" t="inlineStr">
         <is>
-          <t>Remarks</t>
+          <t>Pass/Fail/Not Executed/Blocked</t>
         </is>
       </c>
       <c r="B20" s="16" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>Pass</t>
         </is>
       </c>
     </row>
     <row r="21" ht="15.75" customHeight="1" s="28">
       <c r="A21" s="16" t="inlineStr">
         <is>
-          <t>Executed by</t>
-        </is>
-      </c>
-      <c r="B21" s="9" t="inlineStr">
-        <is>
-          <t>Sammi</t>
+          <t>Remarks</t>
+        </is>
+      </c>
+      <c r="B21" s="16" t="inlineStr">
+        <is>
+          <t>NA</t>
         </is>
       </c>
     </row>
     <row r="22" ht="15.75" customHeight="1" s="28">
       <c r="A22" s="16" t="inlineStr">
         <is>
+          <t>Executed by</t>
+        </is>
+      </c>
+      <c r="B22" s="32" t="inlineStr">
+        <is>
+          <t>Sammi</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="15.75" customHeight="1" s="28">
+      <c r="A23" s="16" t="inlineStr">
+        <is>
           <t>Date of Execution</t>
         </is>
       </c>
-      <c r="B22" s="17" t="n">
+      <c r="B23" s="17" t="n">
         <v>46295</v>
       </c>
     </row>
-    <row r="23" ht="15.75" customHeight="1" s="28"/>
     <row r="24" ht="15.75" customHeight="1" s="28"/>
     <row r="25" ht="15.75" customHeight="1" s="28"/>
     <row r="26" ht="15.75" customHeight="1" s="28"/>
@@ -20891,6 +20945,9 @@
     <row r="999" ht="15.75" customHeight="1" s="28"/>
     <row r="1000" ht="15.75" customHeight="1" s="28"/>
   </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:C1"/>
+  </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
   <pageSetup orientation="landscape"/>
 </worksheet>
@@ -20902,7 +20959,7 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C22"/>
+  <dimension ref="A1:C23"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="12.63" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col width="24.75" customWidth="1" style="28" min="1" max="1"/>
@@ -20910,236 +20967,242 @@
     <col width="12.63" customWidth="1" style="28" min="3" max="6"/>
   </cols>
   <sheetData>
-    <row r="1" ht="15.75" customHeight="1" s="28">
-      <c r="A1" s="2" t="inlineStr">
+    <row r="1" ht="90" customHeight="1" s="28">
+      <c r="A1" s="33" t="inlineStr">
+        <is>
+          <t>v2 (2026-10-20): The Event Operations Manager is now shown as the 'Event Coordinator Lead' (SPM-84 AC1, forum #129, Week 7 Change #5) - the same role, accounts, permissions and pages. Read 'Operations Manager', 'Event Operations Manager' or 'Ops Manager' in this case as 'Event Coordinator Lead'; on screen the role is shown under its new name, and refusals say 'Assigning coordinators is the Event Coordinator Lead's role.'</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="17.25" customHeight="1" s="28">
+      <c r="A2" s="2" t="inlineStr">
         <is>
           <t>Item</t>
         </is>
       </c>
-      <c r="B1" s="5" t="n"/>
-    </row>
-    <row r="2" ht="17.25" customHeight="1" s="28">
-      <c r="A2" s="7" t="inlineStr">
-        <is>
-          <t>Test Case ID</t>
-        </is>
-      </c>
-      <c r="B2" s="9" t="inlineStr">
-        <is>
-          <t>SPM-30-TC02</t>
-        </is>
-      </c>
+      <c r="B2" s="5" t="n"/>
     </row>
     <row r="3" ht="57.75" customHeight="1" s="28">
       <c r="A3" s="7" t="inlineStr">
         <is>
+          <t>Test Case ID</t>
+        </is>
+      </c>
+      <c r="B3" s="32" t="inlineStr">
+        <is>
+          <t>SPM-30-TC02</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="17.25" customHeight="1" s="28">
+      <c r="A4" s="7" t="inlineStr">
+        <is>
           <t>Pre-conditions</t>
         </is>
       </c>
-      <c r="B3" s="9" t="inlineStr">
+      <c r="B4" s="32" t="inlineStr">
         <is>
           <t>Test data freshly loaded: run `npm run fixtures:spm30` from the project folder just before this case.
 Logged in as Nadia Rahman (nadia.rahman@connectsphere.com / password123), Event Operations Manager.</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="17.25" customHeight="1" s="28">
-      <c r="A4" s="7" t="inlineStr">
-        <is>
-          <t>Test Steps</t>
-        </is>
-      </c>
-      <c r="B4" s="9" t="inlineStr">
-        <is>
-          <t>1. Open the Dashboard</t>
-        </is>
-      </c>
-    </row>
     <row r="5" ht="30.75" customHeight="1" s="28">
       <c r="A5" s="7" t="inlineStr">
         <is>
-          <t>Test Data</t>
-        </is>
-      </c>
-      <c r="B5" s="9" t="inlineStr">
-        <is>
-          <t>Expected: SPM30 Nusantara Developer Meetup, SPM30 Meridian Graduate Evening</t>
+          <t>Test Steps</t>
+        </is>
+      </c>
+      <c r="B5" s="32" t="inlineStr">
+        <is>
+          <t>1. Open the Dashboard</t>
         </is>
       </c>
     </row>
     <row r="6" ht="57.75" customHeight="1" s="28">
       <c r="A6" s="7" t="inlineStr">
         <is>
+          <t>Test Data</t>
+        </is>
+      </c>
+      <c r="B6" s="32" t="inlineStr">
+        <is>
+          <t>Expected: SPM30 Nusantara Developer Meetup, SPM30 Meridian Graduate Evening</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="17.25" customHeight="1" s="28">
+      <c r="A7" s="7" t="inlineStr">
+        <is>
           <t>Expected Result</t>
         </is>
       </c>
-      <c r="B6" s="9" t="inlineStr">
+      <c r="B7" s="32" t="inlineStr">
         <is>
           <t>The 'Awaiting assignment' section ('Submitted events with no coordinator yet.') lists 'SPM30 Nusantara Developer Meetup' and 'SPM30 Meridian Graduate Evening'.
 'SPM30 Kirana Regional Offsite' is not listed.</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="17.25" customHeight="1" s="28">
-      <c r="A7" s="7" t="inlineStr">
-        <is>
-          <t>Created By</t>
-        </is>
-      </c>
-      <c r="B7" s="9" t="inlineStr">
-        <is>
-          <t>Kristen</t>
-        </is>
-      </c>
-    </row>
     <row r="8" ht="15.75" customHeight="1" s="28">
       <c r="A8" s="7" t="inlineStr">
         <is>
+          <t>Created By</t>
+        </is>
+      </c>
+      <c r="B8" s="32" t="inlineStr">
+        <is>
+          <t>Kristen</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="15.75" customHeight="1" s="28">
+      <c r="A9" s="7" t="inlineStr">
+        <is>
           <t>Creation Date</t>
         </is>
       </c>
-      <c r="B8" s="17" t="n">
+      <c r="B9" s="17" t="n">
         <v>46293</v>
       </c>
     </row>
-    <row r="9" ht="15.75" customHeight="1" s="28"/>
-    <row r="10" ht="15.75" customHeight="1" s="28">
-      <c r="A10" s="12" t="inlineStr">
+    <row r="10" ht="15.75" customHeight="1" s="28"/>
+    <row r="11" ht="15.75" customHeight="1" s="28">
+      <c r="A11" s="12" t="inlineStr">
         <is>
           <t>Item</t>
         </is>
       </c>
-      <c r="B10" s="13" t="n"/>
-      <c r="C10" s="14" t="n"/>
-    </row>
-    <row r="11" ht="15.75" customHeight="1" s="28">
-      <c r="A11" s="16" t="inlineStr">
+      <c r="B11" s="13" t="n"/>
+      <c r="C11" s="14" t="n"/>
+    </row>
+    <row r="12" ht="15.75" customHeight="1" s="28">
+      <c r="A12" s="16" t="inlineStr">
         <is>
           <t>Actual Result</t>
         </is>
       </c>
-      <c r="B11" s="9" t="inlineStr">
+      <c r="B12" s="32" t="inlineStr">
         <is>
           <t>The 'Awaiting assignment' section ('Submitted events with no coordinator yet.') lists 'SPM30 Nusantara Developer Meetup' and 'SPM30 Meridian Graduate Evening'.
 'SPM30 Kirana Regional Offsite' is not listed.</t>
         </is>
       </c>
     </row>
-    <row r="12" ht="15.75" customHeight="1" s="28">
-      <c r="A12" s="16" t="inlineStr">
-        <is>
-          <t>Pass/Fail/Not Executed/Blocked</t>
-        </is>
-      </c>
-      <c r="B12" s="16" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-    </row>
     <row r="13" ht="15.75" customHeight="1" s="28">
       <c r="A13" s="16" t="inlineStr">
         <is>
-          <t>Remarks</t>
+          <t>Pass/Fail/Not Executed/Blocked</t>
         </is>
       </c>
       <c r="B13" s="16" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>Pass</t>
         </is>
       </c>
     </row>
     <row r="14" ht="15.75" customHeight="1" s="28">
       <c r="A14" s="16" t="inlineStr">
         <is>
-          <t>Executed by</t>
-        </is>
-      </c>
-      <c r="B14" s="9" t="inlineStr">
-        <is>
-          <t>Kristen</t>
+          <t>Remarks</t>
+        </is>
+      </c>
+      <c r="B14" s="16" t="inlineStr">
+        <is>
+          <t>NA</t>
         </is>
       </c>
     </row>
     <row r="15" ht="15.75" customHeight="1" s="28">
       <c r="A15" s="16" t="inlineStr">
         <is>
+          <t>Executed by</t>
+        </is>
+      </c>
+      <c r="B15" s="32" t="inlineStr">
+        <is>
+          <t>Kristen</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="15.75" customHeight="1" s="28">
+      <c r="A16" s="16" t="inlineStr">
+        <is>
           <t>Date of Execution</t>
         </is>
       </c>
-      <c r="B15" s="17" t="n">
+      <c r="B16" s="17" t="n">
         <v>46294</v>
       </c>
     </row>
-    <row r="16" ht="15.75" customHeight="1" s="28"/>
-    <row r="17" ht="15.75" customHeight="1" s="28">
-      <c r="A17" s="12" t="inlineStr">
+    <row r="17" ht="15.75" customHeight="1" s="28"/>
+    <row r="18" ht="15.75" customHeight="1" s="28">
+      <c r="A18" s="12" t="inlineStr">
         <is>
           <t>Item</t>
         </is>
       </c>
-      <c r="B17" s="13" t="n"/>
-    </row>
-    <row r="18" ht="15.75" customHeight="1" s="28">
-      <c r="A18" s="16" t="inlineStr">
+      <c r="B18" s="13" t="n"/>
+    </row>
+    <row r="19" ht="15.75" customHeight="1" s="28">
+      <c r="A19" s="16" t="inlineStr">
         <is>
           <t>Actual Result</t>
         </is>
       </c>
-      <c r="B18" s="9" t="inlineStr">
+      <c r="B19" s="32" t="inlineStr">
         <is>
           <t>The 'Awaiting assignment' section ('Submitted events with no coordinator yet.') lists 'SPM30 Nusantara Developer Meetup' and 'SPM30 Meridian Graduate Evening'.
 'SPM30 Kirana Regional Offsite' is not listed.</t>
         </is>
       </c>
     </row>
-    <row r="19" ht="15.75" customHeight="1" s="28">
-      <c r="A19" s="16" t="inlineStr">
-        <is>
-          <t>Pass/Fail/Not Executed/Blocked</t>
-        </is>
-      </c>
-      <c r="B19" s="16" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-    </row>
     <row r="20" ht="15.75" customHeight="1" s="28">
       <c r="A20" s="16" t="inlineStr">
         <is>
-          <t>Remarks</t>
+          <t>Pass/Fail/Not Executed/Blocked</t>
         </is>
       </c>
       <c r="B20" s="16" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>Pass</t>
         </is>
       </c>
     </row>
     <row r="21" ht="15.75" customHeight="1" s="28">
       <c r="A21" s="16" t="inlineStr">
         <is>
-          <t>Executed by</t>
-        </is>
-      </c>
-      <c r="B21" s="9" t="inlineStr">
-        <is>
-          <t>Sammi</t>
+          <t>Remarks</t>
+        </is>
+      </c>
+      <c r="B21" s="16" t="inlineStr">
+        <is>
+          <t>NA</t>
         </is>
       </c>
     </row>
     <row r="22" ht="15.75" customHeight="1" s="28">
       <c r="A22" s="16" t="inlineStr">
         <is>
+          <t>Executed by</t>
+        </is>
+      </c>
+      <c r="B22" s="32" t="inlineStr">
+        <is>
+          <t>Sammi</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="15.75" customHeight="1" s="28">
+      <c r="A23" s="16" t="inlineStr">
+        <is>
           <t>Date of Execution</t>
         </is>
       </c>
-      <c r="B22" s="17" t="n">
+      <c r="B23" s="17" t="n">
         <v>46295</v>
       </c>
     </row>
-    <row r="23" ht="15.75" customHeight="1" s="28"/>
     <row r="24" ht="15.75" customHeight="1" s="28"/>
     <row r="25" ht="15.75" customHeight="1" s="28"/>
     <row r="26" ht="15.75" customHeight="1" s="28"/>
@@ -22118,6 +22181,9 @@
     <row r="999" ht="15.75" customHeight="1" s="28"/>
     <row r="1000" ht="15.75" customHeight="1" s="28"/>
   </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:C1"/>
+  </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
   <pageSetup orientation="landscape"/>
 </worksheet>
@@ -22129,7 +22195,7 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C22"/>
+  <dimension ref="A1:C23"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="12.63" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col width="24.75" customWidth="1" style="28" min="1" max="1"/>
@@ -22137,46 +22203,53 @@
     <col width="12.63" customWidth="1" style="28" min="3" max="6"/>
   </cols>
   <sheetData>
-    <row r="1" ht="15.75" customHeight="1" s="28">
-      <c r="A1" s="2" t="inlineStr">
+    <row r="1" ht="90" customHeight="1" s="28">
+      <c r="A1" s="33" t="inlineStr">
+        <is>
+          <t>v2 (2026-10-20): The Event Operations Manager is now shown as the 'Event Coordinator Lead' (SPM-84 AC1, forum #129, Week 7 Change #5) - the same role, accounts, permissions and pages. Read 'Operations Manager', 'Event Operations Manager' or 'Ops Manager' in this case as 'Event Coordinator Lead'; on screen the role is shown under its new name, and refusals say 'Assigning coordinators is the Event Coordinator Lead's role.'</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="17.25" customHeight="1" s="28">
+      <c r="A2" s="2" t="inlineStr">
         <is>
           <t>Item</t>
         </is>
       </c>
-      <c r="B1" s="5" t="n"/>
-    </row>
-    <row r="2" ht="17.25" customHeight="1" s="28">
-      <c r="A2" s="7" t="inlineStr">
-        <is>
-          <t>Test Case ID</t>
-        </is>
-      </c>
-      <c r="B2" s="9" t="inlineStr">
-        <is>
-          <t>SPM-30-TC03</t>
-        </is>
-      </c>
+      <c r="B2" s="5" t="n"/>
     </row>
     <row r="3" ht="71.25" customHeight="1" s="28">
       <c r="A3" s="7" t="inlineStr">
         <is>
+          <t>Test Case ID</t>
+        </is>
+      </c>
+      <c r="B3" s="32" t="inlineStr">
+        <is>
+          <t>SPM-30-TC03</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="152.25" customHeight="1" s="28">
+      <c r="A4" s="7" t="inlineStr">
+        <is>
           <t>Pre-conditions</t>
         </is>
       </c>
-      <c r="B3" s="9" t="inlineStr">
+      <c r="B4" s="32" t="inlineStr">
         <is>
           <t>Logged out.
 Accounts: Daniel Tan (daniel.tan@connectsphere.com / password123), Event Coordinator; Budi Santoso (budi.santoso@nusantaratec.com / password123), Event Organiser; Marcus Wong (marcus.wong@connectsphere.com / password123), Venue Staff.</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="152.25" customHeight="1" s="28">
-      <c r="A4" s="7" t="inlineStr">
+    <row r="5" ht="57.75" customHeight="1" s="28">
+      <c r="A5" s="7" t="inlineStr">
         <is>
           <t>Test Steps</t>
         </is>
       </c>
-      <c r="B4" s="9" t="inlineStr">
+      <c r="B5" s="32" t="inlineStr">
         <is>
           <t>1. Log in as Daniel Tan (daniel.tan@connectsphere.com / password123)
 2. Check the sidebar for an 'Assignments' link
@@ -22188,25 +22261,25 @@
         </is>
       </c>
     </row>
-    <row r="5" ht="57.75" customHeight="1" s="28">
-      <c r="A5" s="7" t="inlineStr">
-        <is>
-          <t>Test Data</t>
-        </is>
-      </c>
-      <c r="B5" s="9" t="inlineStr">
-        <is>
-          <t>Event Coordinator: daniel.tan@connectsphere.com / password123 | Event Organiser: budi.santoso@nusantaratec.com / password123 | Venue Staff: marcus.wong@connectsphere.com / password123</t>
-        </is>
-      </c>
-    </row>
     <row r="6" ht="84.75" customHeight="1" s="28">
       <c r="A6" s="7" t="inlineStr">
         <is>
+          <t>Test Data</t>
+        </is>
+      </c>
+      <c r="B6" s="32" t="inlineStr">
+        <is>
+          <t>Event Coordinator: daniel.tan@connectsphere.com / password123 | Event Organiser: budi.santoso@nusantaratec.com / password123 | Venue Staff: marcus.wong@connectsphere.com / password123</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="17.25" customHeight="1" s="28">
+      <c r="A7" s="7" t="inlineStr">
+        <is>
           <t>Expected Result</t>
         </is>
       </c>
-      <c r="B6" s="9" t="inlineStr">
+      <c r="B7" s="32" t="inlineStr">
         <is>
           <t>For each of the three users:
 No 'Assignments' link is shown in the sidebar.
@@ -22215,45 +22288,45 @@
         </is>
       </c>
     </row>
-    <row r="7" ht="17.25" customHeight="1" s="28">
-      <c r="A7" s="7" t="inlineStr">
-        <is>
-          <t>Created By</t>
-        </is>
-      </c>
-      <c r="B7" s="9" t="inlineStr">
-        <is>
-          <t>Kristen</t>
-        </is>
-      </c>
-    </row>
     <row r="8" ht="15.75" customHeight="1" s="28">
       <c r="A8" s="7" t="inlineStr">
         <is>
+          <t>Created By</t>
+        </is>
+      </c>
+      <c r="B8" s="32" t="inlineStr">
+        <is>
+          <t>Kristen</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="15.75" customHeight="1" s="28">
+      <c r="A9" s="7" t="inlineStr">
+        <is>
           <t>Creation Date</t>
         </is>
       </c>
-      <c r="B8" s="17" t="n">
+      <c r="B9" s="17" t="n">
         <v>46293</v>
       </c>
     </row>
-    <row r="9" ht="15.75" customHeight="1" s="28"/>
-    <row r="10" ht="15.75" customHeight="1" s="28">
-      <c r="A10" s="12" t="inlineStr">
+    <row r="10" ht="15.75" customHeight="1" s="28"/>
+    <row r="11" ht="15.75" customHeight="1" s="28">
+      <c r="A11" s="12" t="inlineStr">
         <is>
           <t>Item</t>
         </is>
       </c>
-      <c r="B10" s="13" t="n"/>
-      <c r="C10" s="14" t="n"/>
-    </row>
-    <row r="11" ht="15.75" customHeight="1" s="28">
-      <c r="A11" s="16" t="inlineStr">
+      <c r="B11" s="13" t="n"/>
+      <c r="C11" s="14" t="n"/>
+    </row>
+    <row r="12" ht="15.75" customHeight="1" s="28">
+      <c r="A12" s="16" t="inlineStr">
         <is>
           <t>Actual Result</t>
         </is>
       </c>
-      <c r="B11" s="9" t="inlineStr">
+      <c r="B12" s="32" t="inlineStr">
         <is>
           <t>For each of the three users:
 No 'Assignments' link is shown in the sidebar.
@@ -22262,68 +22335,68 @@
         </is>
       </c>
     </row>
-    <row r="12" ht="15.75" customHeight="1" s="28">
-      <c r="A12" s="16" t="inlineStr">
-        <is>
-          <t>Pass/Fail/Not Executed/Blocked</t>
-        </is>
-      </c>
-      <c r="B12" s="19" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-    </row>
     <row r="13" ht="15.75" customHeight="1" s="28">
       <c r="A13" s="16" t="inlineStr">
         <is>
-          <t>Remarks</t>
-        </is>
-      </c>
-      <c r="B13" s="20" t="inlineStr">
-        <is>
-          <t>NA</t>
+          <t>Pass/Fail/Not Executed/Blocked</t>
+        </is>
+      </c>
+      <c r="B13" s="19" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
     </row>
     <row r="14" ht="15.75" customHeight="1" s="28">
       <c r="A14" s="16" t="inlineStr">
         <is>
-          <t>Executed by</t>
-        </is>
-      </c>
-      <c r="B14" s="21" t="inlineStr">
-        <is>
-          <t>Kristen</t>
+          <t>Remarks</t>
+        </is>
+      </c>
+      <c r="B14" s="20" t="inlineStr">
+        <is>
+          <t>NA</t>
         </is>
       </c>
     </row>
     <row r="15" ht="15.75" customHeight="1" s="28">
       <c r="A15" s="16" t="inlineStr">
         <is>
+          <t>Executed by</t>
+        </is>
+      </c>
+      <c r="B15" s="21" t="inlineStr">
+        <is>
+          <t>Kristen</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="15.75" customHeight="1" s="28">
+      <c r="A16" s="16" t="inlineStr">
+        <is>
           <t>Date of Execution</t>
         </is>
       </c>
-      <c r="B15" s="22" t="n">
+      <c r="B16" s="22" t="n">
         <v>46294</v>
       </c>
     </row>
-    <row r="16" ht="15.75" customHeight="1" s="28"/>
-    <row r="17" ht="15.75" customHeight="1" s="28">
-      <c r="A17" s="12" t="inlineStr">
+    <row r="17" ht="15.75" customHeight="1" s="28"/>
+    <row r="18" ht="15.75" customHeight="1" s="28">
+      <c r="A18" s="12" t="inlineStr">
         <is>
           <t>Item</t>
         </is>
       </c>
-      <c r="B17" s="13" t="n"/>
-    </row>
-    <row r="18" ht="15.75" customHeight="1" s="28">
-      <c r="A18" s="16" t="inlineStr">
+      <c r="B18" s="13" t="n"/>
+    </row>
+    <row r="19" ht="15.75" customHeight="1" s="28">
+      <c r="A19" s="16" t="inlineStr">
         <is>
           <t>Actual Result</t>
         </is>
       </c>
-      <c r="B18" s="9" t="inlineStr">
+      <c r="B19" s="32" t="inlineStr">
         <is>
           <t>For each of the three users:
 No 'Assignments' link is shown in the sidebar.
@@ -22332,53 +22405,52 @@
         </is>
       </c>
     </row>
-    <row r="19" ht="15.75" customHeight="1" s="28">
-      <c r="A19" s="16" t="inlineStr">
-        <is>
-          <t>Pass/Fail/Not Executed/Blocked</t>
-        </is>
-      </c>
-      <c r="B19" s="16" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-    </row>
     <row r="20" ht="15.75" customHeight="1" s="28">
       <c r="A20" s="16" t="inlineStr">
         <is>
-          <t>Remarks</t>
+          <t>Pass/Fail/Not Executed/Blocked</t>
         </is>
       </c>
       <c r="B20" s="16" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>Pass</t>
         </is>
       </c>
     </row>
     <row r="21" ht="15.75" customHeight="1" s="28">
       <c r="A21" s="16" t="inlineStr">
         <is>
-          <t>Executed by</t>
-        </is>
-      </c>
-      <c r="B21" s="9" t="inlineStr">
-        <is>
-          <t>Sammi</t>
+          <t>Remarks</t>
+        </is>
+      </c>
+      <c r="B21" s="16" t="inlineStr">
+        <is>
+          <t>NA</t>
         </is>
       </c>
     </row>
     <row r="22" ht="15.75" customHeight="1" s="28">
       <c r="A22" s="16" t="inlineStr">
         <is>
+          <t>Executed by</t>
+        </is>
+      </c>
+      <c r="B22" s="32" t="inlineStr">
+        <is>
+          <t>Sammi</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="15.75" customHeight="1" s="28">
+      <c r="A23" s="16" t="inlineStr">
+        <is>
           <t>Date of Execution</t>
         </is>
       </c>
-      <c r="B22" s="17" t="n">
+      <c r="B23" s="17" t="n">
         <v>46295</v>
       </c>
     </row>
-    <row r="23" ht="15.75" customHeight="1" s="28"/>
     <row r="24" ht="15.75" customHeight="1" s="28"/>
     <row r="25" ht="15.75" customHeight="1" s="28"/>
     <row r="26" ht="15.75" customHeight="1" s="28"/>
@@ -23357,6 +23429,9 @@
     <row r="999" ht="15.75" customHeight="1" s="28"/>
     <row r="1000" ht="15.75" customHeight="1" s="28"/>
   </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:C1"/>
+  </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
   <pageSetup orientation="landscape"/>
 </worksheet>
@@ -23368,7 +23443,7 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C22"/>
+  <dimension ref="A1:C23"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="12.63" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col width="24.75" customWidth="1" style="28" min="1" max="1"/>
@@ -23376,237 +23451,243 @@
     <col width="12.63" customWidth="1" style="28" min="3" max="6"/>
   </cols>
   <sheetData>
-    <row r="1" ht="15.75" customHeight="1" s="28">
-      <c r="A1" s="2" t="inlineStr">
+    <row r="1" ht="90" customHeight="1" s="28">
+      <c r="A1" s="33" t="inlineStr">
+        <is>
+          <t>v2 (2026-10-20): The Event Operations Manager is now shown as the 'Event Coordinator Lead' (SPM-84 AC1, forum #129, Week 7 Change #5) - the same role, accounts, permissions and pages. Read 'Operations Manager', 'Event Operations Manager' or 'Ops Manager' in this case as 'Event Coordinator Lead'; on screen the role is shown under its new name, and refusals say 'Assigning coordinators is the Event Coordinator Lead's role.'</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="17.25" customHeight="1" s="28">
+      <c r="A2" s="2" t="inlineStr">
         <is>
           <t>Item</t>
         </is>
       </c>
-      <c r="B1" s="5" t="n"/>
-    </row>
-    <row r="2" ht="17.25" customHeight="1" s="28">
-      <c r="A2" s="7" t="inlineStr">
-        <is>
-          <t>Test Case ID</t>
-        </is>
-      </c>
-      <c r="B2" s="9" t="inlineStr">
-        <is>
-          <t>SPM-30-TC04</t>
-        </is>
-      </c>
+      <c r="B2" s="5" t="n"/>
     </row>
     <row r="3" ht="57.75" customHeight="1" s="28">
       <c r="A3" s="7" t="inlineStr">
         <is>
+          <t>Test Case ID</t>
+        </is>
+      </c>
+      <c r="B3" s="32" t="inlineStr">
+        <is>
+          <t>SPM-30-TC04</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="44.25" customHeight="1" s="28">
+      <c r="A4" s="7" t="inlineStr">
+        <is>
           <t>Pre-conditions</t>
         </is>
       </c>
-      <c r="B3" s="9" t="inlineStr">
+      <c r="B4" s="32" t="inlineStr">
         <is>
           <t>Test data loaded: run `npm run fixtures:spm30` from the project folder if it has not been run for this test pass.
 Logged in as Grace Lim (grace.lim@connectsphere.com / password123).</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="44.25" customHeight="1" s="28">
-      <c r="A4" s="7" t="inlineStr">
+    <row r="5" ht="30.75" customHeight="1" s="28">
+      <c r="A5" s="7" t="inlineStr">
         <is>
           <t>Test Steps</t>
         </is>
       </c>
-      <c r="B4" s="9" t="inlineStr">
+      <c r="B5" s="32" t="inlineStr">
         <is>
           <t>1. Click 'Assignments' in the sidebar
 2. Open the 'Assign to' dropdown on the 'SPM30 Meridian Graduate Evening' row</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="30.75" customHeight="1" s="28">
-      <c r="A5" s="7" t="inlineStr">
-        <is>
-          <t>Test Data</t>
-        </is>
-      </c>
-      <c r="B5" s="9" t="inlineStr">
-        <is>
-          <t>Expected options: Daniel Tan, Priya Raj, Joel Fernandez, Hui Shan Neo, Arif Mansor</t>
-        </is>
-      </c>
-    </row>
     <row r="6" ht="57.75" customHeight="1" s="28">
       <c r="A6" s="7" t="inlineStr">
         <is>
+          <t>Test Data</t>
+        </is>
+      </c>
+      <c r="B6" s="32" t="inlineStr">
+        <is>
+          <t>Expected options: Daniel Tan, Priya Raj, Joel Fernandez, Hui Shan Neo, Arif Mansor</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="17.25" customHeight="1" s="28">
+      <c r="A7" s="7" t="inlineStr">
+        <is>
           <t>Expected Result</t>
         </is>
       </c>
-      <c r="B6" s="9" t="inlineStr">
+      <c r="B7" s="32" t="inlineStr">
         <is>
           <t>The dropdown lists exactly the five Event Coordinators.
 No Ops Managers (Grace Lim, Nadia Rahman), Venue Staff (e.g. Marcus Wong), Technical Support (e.g. Kenji Sato), Organisers or Attendees appear.</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="17.25" customHeight="1" s="28">
-      <c r="A7" s="7" t="inlineStr">
-        <is>
-          <t>Created By</t>
-        </is>
-      </c>
-      <c r="B7" s="9" t="inlineStr">
-        <is>
-          <t>Kristen</t>
-        </is>
-      </c>
-    </row>
     <row r="8" ht="15.75" customHeight="1" s="28">
       <c r="A8" s="7" t="inlineStr">
         <is>
+          <t>Created By</t>
+        </is>
+      </c>
+      <c r="B8" s="32" t="inlineStr">
+        <is>
+          <t>Kristen</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="15.75" customHeight="1" s="28">
+      <c r="A9" s="7" t="inlineStr">
+        <is>
           <t>Creation Date</t>
         </is>
       </c>
-      <c r="B8" s="17" t="n">
+      <c r="B9" s="17" t="n">
         <v>46293</v>
       </c>
     </row>
-    <row r="9" ht="15.75" customHeight="1" s="28"/>
-    <row r="10" ht="15.75" customHeight="1" s="28">
-      <c r="A10" s="12" t="inlineStr">
+    <row r="10" ht="15.75" customHeight="1" s="28"/>
+    <row r="11" ht="15.75" customHeight="1" s="28">
+      <c r="A11" s="12" t="inlineStr">
         <is>
           <t>Item</t>
         </is>
       </c>
-      <c r="B10" s="13" t="n"/>
-      <c r="C10" s="14" t="n"/>
-    </row>
-    <row r="11" ht="15.75" customHeight="1" s="28">
-      <c r="A11" s="16" t="inlineStr">
+      <c r="B11" s="13" t="n"/>
+      <c r="C11" s="14" t="n"/>
+    </row>
+    <row r="12" ht="15.75" customHeight="1" s="28">
+      <c r="A12" s="16" t="inlineStr">
         <is>
           <t>Actual Result</t>
         </is>
       </c>
-      <c r="B11" s="9" t="inlineStr">
+      <c r="B12" s="32" t="inlineStr">
         <is>
           <t>The dropdown lists exactly the five Event Coordinators.
 No Ops Managers (Grace Lim, Nadia Rahman), Venue Staff (e.g. Marcus Wong), Technical Support (e.g. Kenji Sato), Organisers or Attendees appear.</t>
         </is>
       </c>
     </row>
-    <row r="12" ht="15.75" customHeight="1" s="28">
-      <c r="A12" s="16" t="inlineStr">
-        <is>
-          <t>Pass/Fail/Not Executed/Blocked</t>
-        </is>
-      </c>
-      <c r="B12" s="23" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-    </row>
     <row r="13" ht="15.75" customHeight="1" s="28">
       <c r="A13" s="16" t="inlineStr">
         <is>
-          <t>Remarks</t>
-        </is>
-      </c>
-      <c r="B13" s="24" t="inlineStr">
-        <is>
-          <t>NA</t>
+          <t>Pass/Fail/Not Executed/Blocked</t>
+        </is>
+      </c>
+      <c r="B13" s="23" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
     </row>
     <row r="14" ht="15.75" customHeight="1" s="28">
       <c r="A14" s="16" t="inlineStr">
         <is>
-          <t>Executed by</t>
-        </is>
-      </c>
-      <c r="B14" s="25" t="inlineStr">
-        <is>
-          <t>Kristen</t>
+          <t>Remarks</t>
+        </is>
+      </c>
+      <c r="B14" s="24" t="inlineStr">
+        <is>
+          <t>NA</t>
         </is>
       </c>
     </row>
     <row r="15" ht="15.75" customHeight="1" s="28">
       <c r="A15" s="16" t="inlineStr">
         <is>
+          <t>Executed by</t>
+        </is>
+      </c>
+      <c r="B15" s="25" t="inlineStr">
+        <is>
+          <t>Kristen</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="15.75" customHeight="1" s="28">
+      <c r="A16" s="16" t="inlineStr">
+        <is>
           <t>Date of Execution</t>
         </is>
       </c>
-      <c r="B15" s="26" t="n">
+      <c r="B16" s="26" t="n">
         <v>46294</v>
       </c>
     </row>
-    <row r="16" ht="15.75" customHeight="1" s="28"/>
-    <row r="17" ht="15.75" customHeight="1" s="28">
-      <c r="A17" s="12" t="inlineStr">
+    <row r="17" ht="15.75" customHeight="1" s="28"/>
+    <row r="18" ht="15.75" customHeight="1" s="28">
+      <c r="A18" s="12" t="inlineStr">
         <is>
           <t>Item</t>
         </is>
       </c>
-      <c r="B17" s="13" t="n"/>
-    </row>
-    <row r="18" ht="15.75" customHeight="1" s="28">
-      <c r="A18" s="16" t="inlineStr">
+      <c r="B18" s="13" t="n"/>
+    </row>
+    <row r="19" ht="15.75" customHeight="1" s="28">
+      <c r="A19" s="16" t="inlineStr">
         <is>
           <t>Actual Result</t>
         </is>
       </c>
-      <c r="B18" s="9" t="inlineStr">
+      <c r="B19" s="32" t="inlineStr">
         <is>
           <t>The dropdown lists exactly the five Event Coordinators.
 No Ops Managers (Grace Lim, Nadia Rahman), Venue Staff (e.g. Marcus Wong), Technical Support (e.g. Kenji Sato), Organisers or Attendees appear.</t>
         </is>
       </c>
     </row>
-    <row r="19" ht="15.75" customHeight="1" s="28">
-      <c r="A19" s="16" t="inlineStr">
-        <is>
-          <t>Pass/Fail/Not Executed/Blocked</t>
-        </is>
-      </c>
-      <c r="B19" s="16" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-    </row>
     <row r="20" ht="15.75" customHeight="1" s="28">
       <c r="A20" s="16" t="inlineStr">
         <is>
-          <t>Remarks</t>
+          <t>Pass/Fail/Not Executed/Blocked</t>
         </is>
       </c>
       <c r="B20" s="16" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>Pass</t>
         </is>
       </c>
     </row>
     <row r="21" ht="15.75" customHeight="1" s="28">
       <c r="A21" s="16" t="inlineStr">
         <is>
-          <t>Executed by</t>
-        </is>
-      </c>
-      <c r="B21" s="9" t="inlineStr">
-        <is>
-          <t>Sammi</t>
+          <t>Remarks</t>
+        </is>
+      </c>
+      <c r="B21" s="16" t="inlineStr">
+        <is>
+          <t>NA</t>
         </is>
       </c>
     </row>
     <row r="22" ht="15.75" customHeight="1" s="28">
       <c r="A22" s="16" t="inlineStr">
         <is>
+          <t>Executed by</t>
+        </is>
+      </c>
+      <c r="B22" s="32" t="inlineStr">
+        <is>
+          <t>Sammi</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="15.75" customHeight="1" s="28">
+      <c r="A23" s="16" t="inlineStr">
+        <is>
           <t>Date of Execution</t>
         </is>
       </c>
-      <c r="B22" s="17" t="n">
+      <c r="B23" s="17" t="n">
         <v>46295</v>
       </c>
     </row>
-    <row r="23" ht="15.75" customHeight="1" s="28"/>
     <row r="24" ht="15.75" customHeight="1" s="28"/>
     <row r="25" ht="15.75" customHeight="1" s="28"/>
     <row r="26" ht="15.75" customHeight="1" s="28"/>
@@ -24585,6 +24666,9 @@
     <row r="999" ht="15.75" customHeight="1" s="28"/>
     <row r="1000" ht="15.75" customHeight="1" s="28"/>
   </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:C1"/>
+  </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
   <pageSetup orientation="landscape"/>
 </worksheet>
@@ -24618,7 +24702,7 @@
           <t>Test Case ID</t>
         </is>
       </c>
-      <c r="B2" s="9" t="inlineStr">
+      <c r="B2" s="32" t="inlineStr">
         <is>
           <t>SPM-30-TC05</t>
         </is>
@@ -24630,7 +24714,7 @@
           <t>Pre-conditions</t>
         </is>
       </c>
-      <c r="B3" s="9" t="inlineStr">
+      <c r="B3" s="32" t="inlineStr">
         <is>
           <t>Test data loaded: run `npm run fixtures:spm30` from the project folder if it has not been run for this test pass.
 'SPM30 Meridian Graduate Evening' is Submitted with no coordinator.
@@ -24644,7 +24728,7 @@
           <t>Test Steps</t>
         </is>
       </c>
-      <c r="B4" s="9" t="inlineStr">
+      <c r="B4" s="32" t="inlineStr">
         <is>
           <t>1. Click 'Assignments' in the sidebar
 2. Leave the 'Assign to' dropdown for 'SPM30 Meridian Graduate Evening' on 'Choose a coordinator'
@@ -24658,7 +24742,7 @@
           <t>Test Data</t>
         </is>
       </c>
-      <c r="B5" s="9" t="inlineStr">
+      <c r="B5" s="32" t="inlineStr">
         <is>
           <t>Coordinator: (none selected)</t>
         </is>
@@ -24670,7 +24754,7 @@
           <t>Expected Result</t>
         </is>
       </c>
-      <c r="B6" s="9" t="inlineStr">
+      <c r="B6" s="32" t="inlineStr">
         <is>
           <t>The 'Assign' button stays disabled while 'Choose a coordinator' is selected.
 The event stays in the 'Awaiting assignment' list with status Submitted.</t>
@@ -24683,7 +24767,7 @@
           <t>Created By</t>
         </is>
       </c>
-      <c r="B7" s="9" t="inlineStr">
+      <c r="B7" s="32" t="inlineStr">
         <is>
           <t>Kristen</t>
         </is>
@@ -24715,7 +24799,7 @@
           <t>Actual Result</t>
         </is>
       </c>
-      <c r="B11" s="9" t="inlineStr">
+      <c r="B11" s="32" t="inlineStr">
         <is>
           <t>The 'Assign' button stays disabled while 'Choose a coordinator' is selected.
 The event stays in the 'Awaiting assignment' list with status Submitted.</t>
@@ -24784,7 +24868,7 @@
           <t>Actual Result</t>
         </is>
       </c>
-      <c r="B19" s="9" t="inlineStr">
+      <c r="B19" s="32" t="inlineStr">
         <is>
           <t>The 'Assign' button stays disabled while 'Choose a coordinator' is selected.
 The event stays in the 'Awaiting assignment' list with status Submitted.</t>
@@ -24821,7 +24905,7 @@
           <t>Executed by</t>
         </is>
       </c>
-      <c r="B22" s="9" t="inlineStr">
+      <c r="B22" s="32" t="inlineStr">
         <is>
           <t>Sammi</t>
         </is>
@@ -25848,7 +25932,7 @@
           <t>Test Case ID</t>
         </is>
       </c>
-      <c r="B2" s="9" t="inlineStr">
+      <c r="B2" s="32" t="inlineStr">
         <is>
           <t>SPM-30-TC06</t>
         </is>
@@ -25860,7 +25944,7 @@
           <t>Pre-conditions</t>
         </is>
       </c>
-      <c r="B3" s="9" t="inlineStr">
+      <c r="B3" s="32" t="inlineStr">
         <is>
           <t>Test data loaded: run `npm run fixtures:spm30` from the project folder if it has not been run for this test pass.
 'SPM30 Meridian Graduate Evening' is Submitted with no coordinator.
@@ -25874,7 +25958,7 @@
           <t>Test Steps</t>
         </is>
       </c>
-      <c r="B4" s="9" t="inlineStr">
+      <c r="B4" s="32" t="inlineStr">
         <is>
           <t>1. Click 'My Events' in the sidebar
 2. Open 'SPM30 Meridian Graduate Evening'</t>
@@ -25887,7 +25971,7 @@
           <t>Test Data</t>
         </is>
       </c>
-      <c r="B5" s="9" t="inlineStr">
+      <c r="B5" s="32" t="inlineStr">
         <is>
           <t>Event: SPM30 Meridian Graduate Evening</t>
         </is>
@@ -25899,7 +25983,7 @@
           <t>Expected Result</t>
         </is>
       </c>
-      <c r="B6" s="9" t="inlineStr">
+      <c r="B6" s="32" t="inlineStr">
         <is>
           <t>The 'Details' card shows Coordinator 'Not yet assigned'.</t>
         </is>
@@ -25911,7 +25995,7 @@
           <t>Created By</t>
         </is>
       </c>
-      <c r="B7" s="9" t="inlineStr">
+      <c r="B7" s="32" t="inlineStr">
         <is>
           <t>Kristen</t>
         </is>
@@ -25943,7 +26027,7 @@
           <t>Actual Result</t>
         </is>
       </c>
-      <c r="B11" s="9" t="inlineStr">
+      <c r="B11" s="32" t="inlineStr">
         <is>
           <t>The 'Details' card shows Coordinator 'Not yet assigned'.</t>
         </is>
@@ -26010,7 +26094,7 @@
           <t>Actual Result</t>
         </is>
       </c>
-      <c r="B18" s="9" t="inlineStr">
+      <c r="B18" s="32" t="inlineStr">
         <is>
           <t>The 'Details' card shows Coordinator 'Not yet assigned'.</t>
         </is>
@@ -26046,7 +26130,7 @@
           <t>Executed by</t>
         </is>
       </c>
-      <c r="B21" s="9" t="inlineStr">
+      <c r="B21" s="32" t="inlineStr">
         <is>
           <t>Sammi</t>
         </is>
@@ -27074,7 +27158,7 @@
           <t>Test Case ID</t>
         </is>
       </c>
-      <c r="B2" s="9" t="inlineStr">
+      <c r="B2" s="32" t="inlineStr">
         <is>
           <t>SPM-30-TC07</t>
         </is>
@@ -27086,7 +27170,7 @@
           <t>Pre-conditions</t>
         </is>
       </c>
-      <c r="B3" s="9" t="inlineStr">
+      <c r="B3" s="32" t="inlineStr">
         <is>
           <t>Test data loaded: run `npm run fixtures:spm30` from the project folder if it has not been run for this test pass.
 'SPM30 Meridian Graduate Evening' is Submitted with no coordinator.
@@ -27100,7 +27184,7 @@
           <t>Test Steps</t>
         </is>
       </c>
-      <c r="B4" s="9" t="inlineStr">
+      <c r="B4" s="32" t="inlineStr">
         <is>
           <t>1. Open the Dashboard
 2. Click 'All Events'
@@ -27115,7 +27199,7 @@
           <t>Test Data</t>
         </is>
       </c>
-      <c r="B5" s="9" t="inlineStr">
+      <c r="B5" s="32" t="inlineStr">
         <is>
           <t>Event: SPM30 Meridian Graduate Evening (unassigned) | Viewer: Daniel Tan</t>
         </is>
@@ -27127,7 +27211,7 @@
           <t>Expected Result</t>
         </is>
       </c>
-      <c r="B6" s="9" t="inlineStr">
+      <c r="B6" s="32" t="inlineStr">
         <is>
           <t>The event does not appear under 'Awaiting your review' on Daniel Tan's dashboard.
 The event details can be viewed and show Coordinator 'Not yet assigned'.
@@ -27141,7 +27225,7 @@
           <t>Created By</t>
         </is>
       </c>
-      <c r="B7" s="9" t="inlineStr">
+      <c r="B7" s="32" t="inlineStr">
         <is>
           <t>Kristen</t>
         </is>
@@ -27173,7 +27257,7 @@
           <t>Actual Result</t>
         </is>
       </c>
-      <c r="B11" s="9" t="inlineStr">
+      <c r="B11" s="32" t="inlineStr">
         <is>
           <t>The event does not appear under 'Awaiting your review' on Daniel Tan's dashboard.
 The event details can be viewed and show Coordinator 'Not yet assigned'.
@@ -27242,7 +27326,7 @@
           <t>Actual Result</t>
         </is>
       </c>
-      <c r="B18" s="9" t="inlineStr">
+      <c r="B18" s="32" t="inlineStr">
         <is>
           <t>The event does not appear under 'Awaiting your review' on Daniel Tan's dashboard.
 The event details can be viewed and show Coordinator 'Not yet assigned'.
@@ -27280,7 +27364,7 @@
           <t>Executed by</t>
         </is>
       </c>
-      <c r="B21" s="9" t="inlineStr">
+      <c r="B21" s="32" t="inlineStr">
         <is>
           <t>Sammi</t>
         </is>
